--- a/database/event/3649/event_3649_evp_summary.xlsx
+++ b/database/event/3649/event_3649_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.6368</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8538</v>
+        <v>3.7722</v>
       </c>
       <c r="E2" t="n">
         <v>10.5827</v>
@@ -548,7 +548,7 @@
         <v>2.3031</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3128</v>
+        <v>3.2387</v>
       </c>
       <c r="E3" t="n">
         <v>9.243399999999999</v>
@@ -594,7 +594,7 @@
         <v>1.993</v>
       </c>
       <c r="D4" t="n">
-        <v>2.81</v>
+        <v>2.7428</v>
       </c>
       <c r="E4" t="n">
         <v>7.9988</v>
@@ -640,7 +640,7 @@
         <v>1.5765</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1348</v>
+        <v>2.0769</v>
       </c>
       <c r="E5" t="n">
         <v>6.3274</v>
@@ -686,7 +686,7 @@
         <v>1.3639</v>
       </c>
       <c r="D6" t="n">
-        <v>1.79</v>
+        <v>1.7369</v>
       </c>
       <c r="E6" t="n">
         <v>5.4739</v>
@@ -732,7 +732,7 @@
         <v>1.0898</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3456</v>
+        <v>1.2987</v>
       </c>
       <c r="E7" t="n">
         <v>4.3739</v>
@@ -778,7 +778,7 @@
         <v>1.0871</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3412</v>
+        <v>1.2943</v>
       </c>
       <c r="E8" t="n">
         <v>4.3631</v>
@@ -824,7 +824,7 @@
         <v>0.8168</v>
       </c>
       <c r="D9" t="n">
-        <v>0.903</v>
+        <v>0.8621</v>
       </c>
       <c r="E9" t="n">
         <v>3.2782</v>
@@ -870,7 +870,7 @@
         <v>0.7955</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.828</v>
       </c>
       <c r="E10" t="n">
         <v>3.1926</v>
@@ -916,7 +916,7 @@
         <v>0.7345</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7695</v>
+        <v>0.7305</v>
       </c>
       <c r="E11" t="n">
         <v>2.9479</v>
@@ -962,7 +962,7 @@
         <v>0.7286</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7599</v>
+        <v>0.7211</v>
       </c>
       <c r="E12" t="n">
         <v>2.9242</v>
@@ -1008,7 +1008,7 @@
         <v>0.5582</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4836</v>
+        <v>0.4486</v>
       </c>
       <c r="E13" t="n">
         <v>2.2402</v>
@@ -1054,7 +1054,7 @@
         <v>0.5077</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4019</v>
+        <v>0.3679</v>
       </c>
       <c r="E14" t="n">
         <v>2.0378</v>
@@ -1100,7 +1100,7 @@
         <v>0.4945</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3803</v>
+        <v>0.3467</v>
       </c>
       <c r="E15" t="n">
         <v>1.9845</v>
@@ -1146,7 +1146,7 @@
         <v>0.4941</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3797</v>
+        <v>0.3461</v>
       </c>
       <c r="E16" t="n">
         <v>1.983</v>
@@ -1192,7 +1192,7 @@
         <v>0.4119</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2465</v>
+        <v>0.2147</v>
       </c>
       <c r="E17" t="n">
         <v>1.6531</v>
@@ -1238,7 +1238,7 @@
         <v>0.3228</v>
       </c>
       <c r="D18" t="n">
-        <v>0.102</v>
+        <v>0.0722</v>
       </c>
       <c r="E18" t="n">
         <v>1.2954</v>
@@ -1284,7 +1284,7 @@
         <v>0.2941</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0555</v>
+        <v>0.0263</v>
       </c>
       <c r="E19" t="n">
         <v>1.1803</v>
@@ -1330,7 +1330,7 @@
         <v>0.1871</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.118</v>
+        <v>-0.1447</v>
       </c>
       <c r="E20" t="n">
         <v>0.751</v>
@@ -1376,7 +1376,7 @@
         <v>0.1226</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2226</v>
+        <v>-0.2479</v>
       </c>
       <c r="E21" t="n">
         <v>0.4921</v>
@@ -1422,7 +1422,7 @@
         <v>0.0866</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2809</v>
+        <v>-0.3054</v>
       </c>
       <c r="E22" t="n">
         <v>0.3476</v>
@@ -1468,7 +1468,7 @@
         <v>0.0818</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2887</v>
+        <v>-0.313</v>
       </c>
       <c r="E23" t="n">
         <v>0.3285</v>
@@ -1514,7 +1514,7 @@
         <v>0.0069</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4103</v>
+        <v>-0.433</v>
       </c>
       <c r="E24" t="n">
         <v>0.0275</v>
@@ -1560,7 +1560,7 @@
         <v>0.0037</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4153</v>
+        <v>-0.438</v>
       </c>
       <c r="E25" t="n">
         <v>0.0149</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0191</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4523</v>
+        <v>-0.4744</v>
       </c>
       <c r="E26" t="n">
         <v>-0.0765</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0307</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4712</v>
+        <v>-0.493</v>
       </c>
       <c r="E27" t="n">
         <v>-0.1233</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0934</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5728</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3748</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0955</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5762</v>
+        <v>-0.5966</v>
       </c>
       <c r="E29" t="n">
         <v>-0.3832</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2179</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7746</v>
+        <v>-0.7923</v>
       </c>
       <c r="E30" t="n">
         <v>-0.8744</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2564</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.837</v>
+        <v>-0.8538</v>
       </c>
       <c r="E31" t="n">
         <v>-1.0289</v>
@@ -1882,7 +1882,7 @@
         <v>-0.3124</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.928</v>
+        <v>-0.9435</v>
       </c>
       <c r="E32" t="n">
         <v>-1.254</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3329</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9611</v>
+        <v>-0.9762</v>
       </c>
       <c r="E33" t="n">
         <v>-1.336</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3684</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0186</v>
+        <v>-1.0329</v>
       </c>
       <c r="E34" t="n">
         <v>-1.4785</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3736</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0272</v>
+        <v>-1.0414</v>
       </c>
       <c r="E35" t="n">
         <v>-1.4996</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3995</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0691</v>
+        <v>-1.0827</v>
       </c>
       <c r="E36" t="n">
         <v>-1.6034</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4086</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0839</v>
+        <v>-1.0973</v>
       </c>
       <c r="E37" t="n">
         <v>-1.6401</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4648</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.175</v>
+        <v>-1.1871</v>
       </c>
       <c r="E38" t="n">
         <v>-1.8655</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4983</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E39" t="n">
         <v>-2</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5748</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3533</v>
+        <v>-1.363</v>
       </c>
       <c r="E40" t="n">
         <v>-2.3069</v>
@@ -2296,7 +2296,7 @@
         <v>-0.7301</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6051</v>
+        <v>-1.6113</v>
       </c>
       <c r="E41" t="n">
         <v>-2.9301</v>

--- a/database/event/3649/event_3649_evp_summary.xlsx
+++ b/database/event/3649/event_3649_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.5827</v>
+        <v>9.156599999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6368</v>
+        <v>2.2815</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7722</v>
+        <v>3.4957</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5827</v>
+        <v>9.156599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1884</v>
+        <v>3.4302</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3943</v>
+        <v>5.7264</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2904</v>
+        <v>6.5996</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4775</v>
+        <v>3.4315</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3943</v>
+        <v>5.7264</v>
       </c>
       <c r="K2" t="n">
         <v>91</v>
@@ -529,7 +529,7 @@
         <v>203</v>
       </c>
       <c r="M2" t="n">
-        <v>9.8718</v>
+        <v>9.1579</v>
       </c>
       <c r="N2" t="n">
         <v>294</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.243399999999999</v>
+        <v>8.116</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3031</v>
+        <v>2.0222</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2387</v>
+        <v>3.026</v>
       </c>
       <c r="E3" t="n">
-        <v>9.243399999999999</v>
+        <v>8.116</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2167</v>
+        <v>3.5163</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0267</v>
+        <v>4.5997</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4042</v>
+        <v>6.9029</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5698</v>
+        <v>3.5892</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0267</v>
+        <v>4.5997</v>
       </c>
       <c r="K3" t="n">
         <v>91</v>
@@ -575,7 +575,7 @@
         <v>203</v>
       </c>
       <c r="M3" t="n">
-        <v>8.596499999999999</v>
+        <v>8.1889</v>
       </c>
       <c r="N3" t="n">
         <v>294</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.9988</v>
+        <v>6.7754</v>
       </c>
       <c r="C4" t="n">
-        <v>1.993</v>
+        <v>1.6882</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7428</v>
+        <v>2.4207</v>
       </c>
       <c r="E4" t="n">
-        <v>7.9988</v>
+        <v>6.7754</v>
       </c>
       <c r="F4" t="n">
-        <v>4.115</v>
+        <v>3.5414</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8838</v>
+        <v>3.234</v>
       </c>
       <c r="H4" t="n">
-        <v>4.115</v>
+        <v>6.9914</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3353</v>
+        <v>3.6352</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8838</v>
+        <v>3.234</v>
       </c>
       <c r="K4" t="n">
         <v>93</v>
@@ -621,7 +621,7 @@
         <v>182</v>
       </c>
       <c r="M4" t="n">
-        <v>7.2191</v>
+        <v>6.8692</v>
       </c>
       <c r="N4" t="n">
         <v>275</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3274</v>
+        <v>5.7155</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5765</v>
+        <v>1.4241</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0769</v>
+        <v>1.9422</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3274</v>
+        <v>5.7155</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5409</v>
+        <v>3.1567</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7865</v>
+        <v>2.5588</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5409</v>
+        <v>5.6359</v>
       </c>
       <c r="I5" t="n">
-        <v>2.87</v>
+        <v>2.9304</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7865</v>
+        <v>2.5588</v>
       </c>
       <c r="K5" t="n">
         <v>91</v>
@@ -667,7 +667,7 @@
         <v>203</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6565</v>
+        <v>5.4892</v>
       </c>
       <c r="N5" t="n">
         <v>294</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4739</v>
+        <v>5.0201</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3639</v>
+        <v>1.2508</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7369</v>
+        <v>1.6283</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4739</v>
+        <v>5.0201</v>
       </c>
       <c r="F6" t="n">
-        <v>4.409</v>
+        <v>4.0796</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0649</v>
+        <v>0.9405</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1781</v>
+        <v>8.887499999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>4.197</v>
+        <v>4.6211</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0649</v>
+        <v>0.9405</v>
       </c>
       <c r="K6" t="n">
         <v>93</v>
@@ -713,7 +713,7 @@
         <v>182</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2619</v>
+        <v>5.5616</v>
       </c>
       <c r="N6" t="n">
         <v>275</v>
@@ -722,47 +722,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3739</v>
+        <v>4.5026</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0898</v>
+        <v>1.1219</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2987</v>
+        <v>1.3947</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3739</v>
+        <v>4.5026</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4913</v>
+        <v>2.0492</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1174</v>
+        <v>2.4534</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5089</v>
+        <v>2.0492</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4651</v>
+        <v>1.0655</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1174</v>
+        <v>2.4534</v>
       </c>
       <c r="K7" t="n">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="L7" t="n">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3477</v>
+        <v>3.518899999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>201</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3631</v>
+        <v>4.3195</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0871</v>
+        <v>1.0762</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2943</v>
+        <v>1.312</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3631</v>
+        <v>4.3195</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3495</v>
+        <v>4.0251</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0136</v>
+        <v>0.2944</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9386</v>
+        <v>8.695600000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0029</v>
+        <v>4.5213</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0136</v>
+        <v>0.2944</v>
       </c>
       <c r="K8" t="n">
         <v>93</v>
@@ -805,7 +805,7 @@
         <v>182</v>
       </c>
       <c r="M8" t="n">
-        <v>4.016500000000001</v>
+        <v>4.8157</v>
       </c>
       <c r="N8" t="n">
         <v>275</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2782</v>
+        <v>4.0652</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8168</v>
+        <v>1.0129</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8621</v>
+        <v>1.1972</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2782</v>
+        <v>4.0652</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0733</v>
+        <v>4.1961</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7951</v>
+        <v>-0.1309</v>
       </c>
       <c r="H9" t="n">
-        <v>4.0733</v>
+        <v>9.2981</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3015</v>
+        <v>4.8346</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7951</v>
+        <v>-0.1309</v>
       </c>
       <c r="K9" t="n">
         <v>150</v>
@@ -851,7 +851,7 @@
         <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5064</v>
+        <v>4.7037</v>
       </c>
       <c r="N9" t="n">
         <v>201</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1926</v>
+        <v>3.0382</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7955</v>
+        <v>0.757</v>
       </c>
       <c r="D10" t="n">
-        <v>0.828</v>
+        <v>0.7336</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1926</v>
+        <v>3.0382</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7866</v>
+        <v>3.4304</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.594</v>
+        <v>-0.3922</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7866</v>
+        <v>6.6002</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0691</v>
+        <v>3.4318</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.594</v>
+        <v>-0.3922</v>
       </c>
       <c r="K10" t="n">
         <v>157</v>
@@ -897,7 +897,7 @@
         <v>72</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4751</v>
+        <v>3.0396</v>
       </c>
       <c r="N10" t="n">
         <v>229</v>
@@ -906,216 +906,216 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9479</v>
+        <v>2.9932</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7345</v>
+        <v>0.7458</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7305</v>
+        <v>0.7133</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9479</v>
+        <v>2.9932</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9366</v>
+        <v>2.9932</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0113</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9366</v>
+        <v>3.2127</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7591</v>
+        <v>3.2127</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0113</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="L11" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7704</v>
+        <v>3.2127</v>
       </c>
       <c r="N11" t="n">
-        <v>294</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9242</v>
+        <v>2.9799</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7286</v>
+        <v>0.7425</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7211</v>
+        <v>0.7073</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9242</v>
+        <v>2.9799</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9242</v>
+        <v>3.5039</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.524</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9242</v>
+        <v>6.8593</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9242</v>
+        <v>3.5665</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.524</v>
       </c>
       <c r="K12" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9242</v>
+        <v>3.0425</v>
       </c>
       <c r="N12" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2402</v>
+        <v>2.8783</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5582</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4486</v>
+        <v>0.6614</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2402</v>
+        <v>2.8783</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9711</v>
+        <v>2.8783</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7309</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9711</v>
+        <v>2.9605</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4081</v>
+        <v>2.9605</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7309</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="L13" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6772</v>
+        <v>2.9605</v>
       </c>
       <c r="N13" t="n">
-        <v>229</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0378</v>
+        <v>2.6408</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5077</v>
+        <v>0.658</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3679</v>
+        <v>0.5542</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0378</v>
+        <v>2.6408</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0378</v>
+        <v>2.6921</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.0513</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0378</v>
+        <v>3.999</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0378</v>
+        <v>2.0793</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.0513</v>
       </c>
       <c r="K14" t="n">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0378</v>
+        <v>2.028</v>
       </c>
       <c r="N14" t="n">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9845</v>
+        <v>2.539</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4945</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3467</v>
+        <v>0.5082</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9845</v>
+        <v>2.539</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9845</v>
+        <v>2.539</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9845</v>
+        <v>2.539</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9845</v>
+        <v>2.539</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9845</v>
+        <v>2.539</v>
       </c>
       <c r="N15" t="n">
         <v>184</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.983</v>
+        <v>2.5247</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4941</v>
+        <v>0.6291</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3461</v>
+        <v>0.5018</v>
       </c>
       <c r="E16" t="n">
-        <v>1.983</v>
+        <v>2.5247</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9806</v>
+        <v>2.5247</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9806</v>
+        <v>2.5247</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6053</v>
+        <v>2.5247</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="L16" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6077</v>
+        <v>2.5247</v>
       </c>
       <c r="N16" t="n">
-        <v>201</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6531</v>
+        <v>2.509</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4119</v>
+        <v>0.6251</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2147</v>
+        <v>0.4947</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6531</v>
+        <v>2.509</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6531</v>
+        <v>2.9052</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>-0.3962</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6531</v>
+        <v>4.7498</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1504</v>
+        <v>2.4697</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>-0.3962</v>
       </c>
       <c r="K17" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1504</v>
+        <v>2.0735</v>
       </c>
       <c r="N17" t="n">
-        <v>201</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2954</v>
+        <v>2.2373</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3228</v>
+        <v>0.5574</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0722</v>
+        <v>0.372</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2954</v>
+        <v>2.2373</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2954</v>
+        <v>2.9944</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.7571</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2954</v>
+        <v>5.0641</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2954</v>
+        <v>2.6331</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.7571</v>
       </c>
       <c r="K18" t="n">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2954</v>
+        <v>1.876</v>
       </c>
       <c r="N18" t="n">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1803</v>
+        <v>1.9715</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2941</v>
+        <v>0.4912</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0263</v>
+        <v>0.252</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1803</v>
+        <v>1.9715</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5206</v>
+        <v>1.2915</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6597</v>
+        <v>0.68</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5206</v>
+        <v>1.2915</v>
       </c>
       <c r="I19" t="n">
-        <v>0.422</v>
+        <v>0.6715</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6597</v>
+        <v>0.68</v>
       </c>
       <c r="K19" t="n">
         <v>157</v>
@@ -1311,7 +1311,7 @@
         <v>72</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0817</v>
+        <v>1.3515</v>
       </c>
       <c r="N19" t="n">
         <v>229</v>
@@ -1320,78 +1320,78 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.751</v>
+        <v>1.2498</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1871</v>
+        <v>0.3114</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1447</v>
+        <v>-0.0738</v>
       </c>
       <c r="E20" t="n">
-        <v>0.751</v>
+        <v>1.2498</v>
       </c>
       <c r="F20" t="n">
-        <v>0.751</v>
+        <v>1.8784</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.6286</v>
       </c>
       <c r="H20" t="n">
-        <v>0.751</v>
+        <v>1.8784</v>
       </c>
       <c r="I20" t="n">
-        <v>0.751</v>
+        <v>0.9767</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.6286</v>
       </c>
       <c r="K20" t="n">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="M20" t="n">
-        <v>0.751</v>
+        <v>0.3481</v>
       </c>
       <c r="N20" t="n">
-        <v>155</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4921</v>
+        <v>1.172</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1226</v>
+        <v>0.292</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2479</v>
+        <v>-0.1089</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4921</v>
+        <v>1.172</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4921</v>
+        <v>1.172</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4921</v>
+        <v>1.172</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4921</v>
+        <v>1.172</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4921</v>
+        <v>1.172</v>
       </c>
       <c r="N21" t="n">
         <v>155</v>
@@ -1412,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3476</v>
+        <v>0.9579</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0866</v>
+        <v>0.2387</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3054</v>
+        <v>-0.2056</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3476</v>
+        <v>0.9579</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3476</v>
+        <v>1.0274</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3476</v>
+        <v>1.0274</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3476</v>
+        <v>0.5342</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3476</v>
+        <v>0.4647</v>
       </c>
       <c r="N22" t="n">
-        <v>120</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3285</v>
+        <v>0.7029</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0818</v>
+        <v>0.1751</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.313</v>
+        <v>-0.3207</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3285</v>
+        <v>0.7029</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1482</v>
+        <v>0.7029</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4767</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1482</v>
+        <v>0.7029</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1201</v>
+        <v>0.7029</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4767</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="L23" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3566</v>
+        <v>0.7029</v>
       </c>
       <c r="N23" t="n">
-        <v>275</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0275</v>
+        <v>0.5401</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0069</v>
+        <v>0.1346</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.433</v>
+        <v>-0.3942</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0275</v>
+        <v>0.5401</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0275</v>
+        <v>0.5401</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0275</v>
+        <v>0.5401</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0275</v>
+        <v>0.5401</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0275</v>
+        <v>0.5401</v>
       </c>
       <c r="N24" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0149</v>
+        <v>0.4876</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0037</v>
+        <v>0.1215</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.438</v>
+        <v>-0.4179</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0149</v>
+        <v>0.4876</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0149</v>
+        <v>0.4876</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0149</v>
+        <v>0.4876</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0149</v>
+        <v>0.4876</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0149</v>
+        <v>0.4876</v>
       </c>
       <c r="N25" t="n">
         <v>120</v>
@@ -1596,415 +1596,415 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0765</v>
+        <v>0.4566</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0191</v>
+        <v>0.1138</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4744</v>
+        <v>-0.4319</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0765</v>
+        <v>0.4566</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.2835</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9843</v>
+        <v>0.1731</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.2835</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7358</v>
+        <v>0.1474</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9843</v>
+        <v>0.1731</v>
       </c>
       <c r="K26" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L26" t="n">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2484999999999999</v>
+        <v>0.3205</v>
       </c>
       <c r="N26" t="n">
-        <v>294</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1233</v>
+        <v>0.3887</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0307</v>
+        <v>0.0968</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.493</v>
+        <v>-0.4625</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1233</v>
+        <v>0.3887</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1233</v>
+        <v>0.3887</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1233</v>
+        <v>0.3887</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1233</v>
+        <v>0.3887</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1233</v>
+        <v>0.3887</v>
       </c>
       <c r="N27" t="n">
-        <v>155</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3748</v>
+        <v>0.3644</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0934</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.4735</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3748</v>
+        <v>0.3644</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3748</v>
+        <v>0.3644</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3748</v>
+        <v>0.3644</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3748</v>
+        <v>0.3644</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3748</v>
+        <v>0.3644</v>
       </c>
       <c r="N28" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3832</v>
+        <v>-0.1548</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0955</v>
+        <v>-0.0386</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5966</v>
+        <v>-0.7079</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3832</v>
+        <v>-0.1548</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1334</v>
+        <v>1.1484</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2498</v>
+        <v>-1.3032</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1334</v>
+        <v>1.1484</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1081</v>
+        <v>0.5971</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2498</v>
+        <v>-1.3032</v>
       </c>
       <c r="K29" t="n">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="L29" t="n">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3579</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>201</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.8744</v>
+        <v>-0.2256</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2179</v>
+        <v>-0.0562</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7923</v>
+        <v>-0.7399</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.8744</v>
+        <v>-0.2256</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1928</v>
+        <v>-0.2256</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6816</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1928</v>
+        <v>-0.2256</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1563</v>
+        <v>-0.2256</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6816</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="L30" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.8379</v>
+        <v>-0.2256</v>
       </c>
       <c r="N30" t="n">
-        <v>229</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0289</v>
+        <v>-0.3667</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2564</v>
+        <v>-0.0914</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8538</v>
+        <v>-0.8036</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0289</v>
+        <v>-0.3667</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0289</v>
+        <v>-0.3667</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0289</v>
+        <v>-0.3667</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0289</v>
+        <v>-0.3667</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.0289</v>
+        <v>-0.3667</v>
       </c>
       <c r="N31" t="n">
-        <v>184</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.254</v>
+        <v>-0.4768</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3124</v>
+        <v>-0.1188</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9435</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.254</v>
+        <v>-0.4768</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4233</v>
+        <v>-0.065</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.6773</v>
+        <v>-0.4118</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4233</v>
+        <v>-0.065</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3431</v>
+        <v>-0.0338</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.6773</v>
+        <v>-0.4118</v>
       </c>
       <c r="K32" t="n">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="L32" t="n">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.3342</v>
+        <v>-0.4456</v>
       </c>
       <c r="N32" t="n">
-        <v>275</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.336</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3329</v>
+        <v>-0.1717</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9762</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.336</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.336</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.336</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.336</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.336</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>120</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.4785</v>
+        <v>-0.8786</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3684</v>
+        <v>-0.2189</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0329</v>
+        <v>-1.0347</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.4785</v>
+        <v>-0.8786</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.4785</v>
+        <v>-0.8786</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.4785</v>
+        <v>-0.8786</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.4785</v>
+        <v>-0.8786</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.4785</v>
+        <v>-0.8786</v>
       </c>
       <c r="N34" t="n">
-        <v>184</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.4996</v>
+        <v>-1.0847</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3736</v>
+        <v>-0.2703</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0414</v>
+        <v>-1.1277</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.4996</v>
+        <v>-1.0847</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.4996</v>
+        <v>-1.0847</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.4996</v>
+        <v>-1.0847</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.4996</v>
+        <v>-1.0847</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.4996</v>
+        <v>-1.0847</v>
       </c>
       <c r="N35" t="n">
         <v>86</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6034</v>
+        <v>-1.2588</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3995</v>
+        <v>-0.3136</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0827</v>
+        <v>-1.2063</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6034</v>
+        <v>-1.2588</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.6034</v>
+        <v>-1.2588</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.6034</v>
+        <v>-1.2588</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.6034</v>
+        <v>-1.2588</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6034</v>
+        <v>-1.2588</v>
       </c>
       <c r="N36" t="n">
         <v>86</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6401</v>
+        <v>-1.2712</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4086</v>
+        <v>-0.3167</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0973</v>
+        <v>-1.2119</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6401</v>
+        <v>-1.2712</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6401</v>
+        <v>-1.2712</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6401</v>
+        <v>-1.2712</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.6401</v>
+        <v>-1.2712</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.6401</v>
+        <v>-1.2712</v>
       </c>
       <c r="N37" t="n">
         <v>86</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.8655</v>
+        <v>-1.315</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4648</v>
+        <v>-0.3276</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1871</v>
+        <v>-1.2317</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.8655</v>
+        <v>-1.315</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.8655</v>
+        <v>-1.315</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.8655</v>
+        <v>-1.315</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.8655</v>
+        <v>-1.315</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.8655</v>
+        <v>-1.315</v>
       </c>
       <c r="N38" t="n">
         <v>86</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BIT</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2</v>
+        <v>-1.7858</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4983</v>
+        <v>-0.4449</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2407</v>
+        <v>-1.4442</v>
       </c>
       <c r="E39" t="n">
-        <v>-2</v>
+        <v>-1.7858</v>
       </c>
       <c r="F39" t="n">
-        <v>-2</v>
+        <v>-1.2136</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.5722</v>
       </c>
       <c r="H39" t="n">
-        <v>-2</v>
+        <v>-1.2136</v>
       </c>
       <c r="I39" t="n">
-        <v>-2</v>
+        <v>-0.631</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.5722</v>
       </c>
       <c r="K39" t="n">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M39" t="n">
-        <v>-2</v>
+        <v>-1.2032</v>
       </c>
       <c r="N39" t="n">
-        <v>120</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>BIT</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3069</v>
+        <v>-1.8795</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5748</v>
+        <v>-0.4683</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.363</v>
+        <v>-1.4865</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3069</v>
+        <v>-1.8795</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4271</v>
+        <v>-1.8795</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8798</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4271</v>
+        <v>-1.8795</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1567</v>
+        <v>-1.8795</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8798</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="L40" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0365</v>
+        <v>-1.8795</v>
       </c>
       <c r="N40" t="n">
-        <v>229</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.9301</v>
+        <v>-2.2699</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7301</v>
+        <v>-0.5656</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6113</v>
+        <v>-1.6628</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.9301</v>
+        <v>-2.2699</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.9301</v>
+        <v>-2.2699</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.9301</v>
+        <v>-2.2699</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.9301</v>
+        <v>-2.2699</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.9301</v>
+        <v>-2.2699</v>
       </c>
       <c r="N41" t="n">
         <v>155</v>
@@ -2429,10 +2429,10 @@
         <v>1.55</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2442</v>
+        <v>1.1703</v>
       </c>
       <c r="J2" t="n">
-        <v>27.3724</v>
+        <v>25.7466</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.54</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2243</v>
+        <v>1.1582</v>
       </c>
       <c r="J3" t="n">
-        <v>26.9346</v>
+        <v>25.4804</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9263</v>
+        <v>0.9706</v>
       </c>
       <c r="J4" t="n">
-        <v>20.3786</v>
+        <v>21.3532</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.26</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5738</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>12.6236</v>
+        <v>14.7818</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0596</v>
+        <v>0.1461</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3112</v>
+        <v>3.2142</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1877</v>
+        <v>0.1681</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1294</v>
+        <v>3.6982</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1654</v>
+        <v>0.1401</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6388</v>
+        <v>3.0822</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3799</v>
+        <v>-0.2597</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.357799999999999</v>
+        <v>-5.7134</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.61</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3915</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.9184</v>
+        <v>-8.613</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.46</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7786</v>
+        <v>-0.5308</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.1292</v>
+        <v>-11.6776</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1975</v>
+        <v>0.1519</v>
       </c>
       <c r="J12" t="n">
-        <v>5.925</v>
+        <v>4.557</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1597</v>
+        <v>0.1172</v>
       </c>
       <c r="J13" t="n">
-        <v>4.791</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1597</v>
+        <v>0.1172</v>
       </c>
       <c r="J14" t="n">
-        <v>4.791</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3232</v>
+        <v>-0.2018</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.696</v>
+        <v>-6.054</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.71</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4955</v>
+        <v>-0.3199</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.865</v>
+        <v>-9.597</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.31</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4809</v>
+        <v>0.4165</v>
       </c>
       <c r="J17" t="n">
-        <v>14.427</v>
+        <v>12.495</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4809</v>
+        <v>0.4165</v>
       </c>
       <c r="J18" t="n">
-        <v>14.427</v>
+        <v>12.495</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3701</v>
+        <v>0.3214</v>
       </c>
       <c r="J19" t="n">
-        <v>11.103</v>
+        <v>9.641999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.03</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0178</v>
+        <v>0.0473</v>
       </c>
       <c r="J20" t="n">
-        <v>0.534</v>
+        <v>1.419</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.93</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2171</v>
+        <v>-0.1171</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.513</v>
+        <v>-3.513</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.44</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7183</v>
+        <v>0.6814</v>
       </c>
       <c r="J22" t="n">
-        <v>20.1124</v>
+        <v>19.0792</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2545</v>
+        <v>0.2041</v>
       </c>
       <c r="J23" t="n">
-        <v>7.126</v>
+        <v>5.7148</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2541</v>
+        <v>-0.1589</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.1148</v>
+        <v>-4.4492</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.68</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.3469</v>
       </c>
       <c r="J25" t="n">
-        <v>-14.9184</v>
+        <v>-9.713200000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6838</v>
+        <v>-0.4582</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.1464</v>
+        <v>-12.8296</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0.598</v>
+        <v>0.5221</v>
       </c>
       <c r="J27" t="n">
-        <v>16.744</v>
+        <v>14.6188</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.21</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3442</v>
+        <v>0.2984</v>
       </c>
       <c r="J28" t="n">
-        <v>9.637600000000001</v>
+        <v>8.3552</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.19</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3133</v>
+        <v>0.2737</v>
       </c>
       <c r="J29" t="n">
-        <v>8.772399999999999</v>
+        <v>7.6636</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0979</v>
+        <v>0.1139</v>
       </c>
       <c r="J30" t="n">
-        <v>2.7412</v>
+        <v>3.1892</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2809</v>
+        <v>-0.1616</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.8652</v>
+        <v>-4.5248</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.72</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5667</v>
+        <v>1.3742</v>
       </c>
       <c r="J32" t="n">
-        <v>39.1675</v>
+        <v>34.355</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.59</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3234</v>
+        <v>1.2191</v>
       </c>
       <c r="J33" t="n">
-        <v>33.085</v>
+        <v>30.4775</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.29</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6458</v>
+        <v>0.7411</v>
       </c>
       <c r="J34" t="n">
-        <v>16.145</v>
+        <v>18.5275</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.649</v>
       </c>
       <c r="J35" t="n">
-        <v>13.7725</v>
+        <v>16.225</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3726</v>
+        <v>-0.2878</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.315</v>
+        <v>-7.195</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.92</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0725</v>
+        <v>-0.0819</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.8125</v>
+        <v>-2.0475</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.87</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.16</v>
+        <v>-0.1398</v>
       </c>
       <c r="J38" t="n">
-        <v>-4</v>
+        <v>-3.495</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.87</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.16</v>
+        <v>-0.1398</v>
       </c>
       <c r="J39" t="n">
-        <v>-4</v>
+        <v>-3.495</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3403</v>
+        <v>-0.241</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.5075</v>
+        <v>-6.025</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.43</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8144</v>
+        <v>-0.5581</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.36</v>
+        <v>-13.9525</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.64</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4774</v>
+        <v>1.309</v>
       </c>
       <c r="J42" t="n">
-        <v>38.4124</v>
+        <v>34.034</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.51</v>
       </c>
       <c r="I43" t="n">
-        <v>1.2265</v>
+        <v>1.1465</v>
       </c>
       <c r="J43" t="n">
-        <v>31.889</v>
+        <v>29.809</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.51</v>
       </c>
       <c r="I44" t="n">
-        <v>1.2265</v>
+        <v>1.1465</v>
       </c>
       <c r="J44" t="n">
-        <v>31.889</v>
+        <v>29.809</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.82</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6898</v>
+        <v>-0.6306</v>
       </c>
       <c r="J45" t="n">
-        <v>-17.9348</v>
+        <v>-16.3956</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.0042</v>
+        <v>-0.9795</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.1092</v>
+        <v>-25.467</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.28</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5339</v>
+        <v>0.6319</v>
       </c>
       <c r="J47" t="n">
-        <v>13.8814</v>
+        <v>16.4294</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.01</v>
       </c>
       <c r="I48" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>2.4128</v>
+        <v>1.6562</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.76</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4117</v>
+        <v>-0.2648</v>
       </c>
       <c r="J49" t="n">
-        <v>-10.7042</v>
+        <v>-6.8848</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4963</v>
+        <v>-0.3226</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.9038</v>
+        <v>-8.387600000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5099</v>
+        <v>-0.3321</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.2574</v>
+        <v>-8.634600000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.53</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2749</v>
+        <v>0.9025</v>
       </c>
       <c r="J52" t="n">
-        <v>29.3227</v>
+        <v>20.7575</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.43</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0719</v>
+        <v>0.7743</v>
       </c>
       <c r="J53" t="n">
-        <v>24.6537</v>
+        <v>17.8089</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6856</v>
+        <v>0.5483</v>
       </c>
       <c r="J54" t="n">
-        <v>15.7688</v>
+        <v>12.6109</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1284</v>
+        <v>-0.0521</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.9532</v>
+        <v>-1.1983</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.85</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6115</v>
+        <v>-0.5465</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.0645</v>
+        <v>-12.5695</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.08</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2627</v>
+        <v>0.2665</v>
       </c>
       <c r="J57" t="n">
-        <v>6.0421</v>
+        <v>6.1295</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.99</v>
       </c>
       <c r="I58" t="n">
-        <v>0.051</v>
+        <v>0.0076</v>
       </c>
       <c r="J58" t="n">
-        <v>1.173</v>
+        <v>0.1748</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0259</v>
+        <v>-0.0123</v>
       </c>
       <c r="J59" t="n">
-        <v>0.5957</v>
+        <v>-0.2829</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.7</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4773</v>
+        <v>-0.3136</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.9779</v>
+        <v>-7.2128</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.36</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.9029</v>
+        <v>-0.6274</v>
       </c>
       <c r="J61" t="n">
-        <v>-20.7667</v>
+        <v>-14.4302</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.39</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0129</v>
+        <v>0.7327</v>
       </c>
       <c r="J62" t="n">
-        <v>28.3612</v>
+        <v>20.5156</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.23</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6427</v>
+        <v>0.5135</v>
       </c>
       <c r="J63" t="n">
-        <v>17.9956</v>
+        <v>14.378</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4758</v>
+        <v>0.4277</v>
       </c>
       <c r="J64" t="n">
-        <v>13.3224</v>
+        <v>11.9756</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.15</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4048</v>
+        <v>0.3988</v>
       </c>
       <c r="J65" t="n">
-        <v>11.3344</v>
+        <v>11.1664</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5196</v>
+        <v>-0.4514</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.5488</v>
+        <v>-12.6392</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0486</v>
+        <v>-0.0589</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.3608</v>
+        <v>-1.6492</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1433</v>
+        <v>-0.1186</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.0124</v>
+        <v>-3.3208</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.89</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1616</v>
+        <v>-0.1297</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.5248</v>
+        <v>-3.6316</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3178</v>
+        <v>-0.2104</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.898400000000001</v>
+        <v>-5.8912</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.68</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5125</v>
+        <v>-0.336</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.35</v>
+        <v>-9.407999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>1.887</v>
+        <v>1.4067</v>
       </c>
       <c r="J72" t="n">
-        <v>35.853</v>
+        <v>26.7273</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.5</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1093</v>
+        <v>0.8268</v>
       </c>
       <c r="J73" t="n">
-        <v>21.0767</v>
+        <v>15.7092</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.42</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9152</v>
+        <v>0.7316</v>
       </c>
       <c r="J74" t="n">
-        <v>17.3888</v>
+        <v>13.9004</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.26</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5471</v>
+        <v>0.5251</v>
       </c>
       <c r="J75" t="n">
-        <v>10.3949</v>
+        <v>9.976900000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.96</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3556</v>
+        <v>-0.2686</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.7564</v>
+        <v>-5.1034</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.05</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2523</v>
+        <v>0.2521</v>
       </c>
       <c r="J77" t="n">
-        <v>4.7937</v>
+        <v>4.7899</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.04</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2326</v>
+        <v>0.2262</v>
       </c>
       <c r="J78" t="n">
-        <v>4.4194</v>
+        <v>4.2978</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.6</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5837</v>
+        <v>-0.3925</v>
       </c>
       <c r="J79" t="n">
-        <v>-11.0903</v>
+        <v>-7.4575</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.59</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5976</v>
+        <v>-0.4018</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.3544</v>
+        <v>-7.6342</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.32</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.653</v>
       </c>
       <c r="J81" t="n">
-        <v>-17.784</v>
+        <v>-12.407</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7214</v>
+        <v>0.54</v>
       </c>
       <c r="J82" t="n">
-        <v>21.642</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.21</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4021</v>
+        <v>0.3444</v>
       </c>
       <c r="J83" t="n">
-        <v>12.063</v>
+        <v>10.332</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.224</v>
+        <v>-0.1329</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.72</v>
+        <v>-3.987</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3952</v>
+        <v>-0.2476</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.856</v>
+        <v>-7.428</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.58</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6683</v>
+        <v>-0.4462</v>
       </c>
       <c r="J86" t="n">
-        <v>-20.049</v>
+        <v>-13.386</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4853</v>
+        <v>0.3794</v>
       </c>
       <c r="J87" t="n">
-        <v>14.559</v>
+        <v>11.382</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2687</v>
+        <v>0.2205</v>
       </c>
       <c r="J88" t="n">
-        <v>8.061</v>
+        <v>6.615</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.02</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0258</v>
+        <v>0.0407</v>
       </c>
       <c r="J89" t="n">
-        <v>0.774</v>
+        <v>1.221</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.01</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0002</v>
+        <v>0.0203</v>
       </c>
       <c r="J90" t="n">
-        <v>0.006</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.87</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2943</v>
+        <v>-0.1742</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.829000000000001</v>
+        <v>-5.226</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.66</v>
       </c>
       <c r="I92" t="n">
-        <v>1.5194</v>
+        <v>1.0629</v>
       </c>
       <c r="J92" t="n">
-        <v>34.9462</v>
+        <v>24.4467</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.29</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7548</v>
+        <v>0.5878</v>
       </c>
       <c r="J93" t="n">
-        <v>17.3604</v>
+        <v>13.5194</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.14</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3377</v>
+        <v>0.3766</v>
       </c>
       <c r="J94" t="n">
-        <v>7.7671</v>
+        <v>8.661799999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0413</v>
+        <v>0.1138</v>
       </c>
       <c r="J95" t="n">
-        <v>0.9499</v>
+        <v>2.6174</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.98</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2312</v>
+        <v>-0.1502</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.3176</v>
+        <v>-3.4546</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3816</v>
+        <v>0.3872</v>
       </c>
       <c r="J97" t="n">
-        <v>8.7768</v>
+        <v>8.9056</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.9</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1433</v>
+        <v>-0.1186</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.2959</v>
+        <v>-2.7278</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.83</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2824</v>
+        <v>-0.1907</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.4952</v>
+        <v>-4.3861</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3666</v>
+        <v>-0.2398</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.431800000000001</v>
+        <v>-5.5154</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6692</v>
+        <v>-0.4482</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.3916</v>
+        <v>-10.3086</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4048</v>
+        <v>0.46</v>
       </c>
       <c r="J102" t="n">
-        <v>11.3344</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0355</v>
+        <v>0.0104</v>
       </c>
       <c r="J103" t="n">
-        <v>0.994</v>
+        <v>0.2912</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.95</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0958</v>
+        <v>-0.0711</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.6824</v>
+        <v>-1.9908</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.79</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3829</v>
+        <v>-0.2418</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.7212</v>
+        <v>-6.7704</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.76</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4261</v>
+        <v>-0.2714</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.9308</v>
+        <v>-7.5992</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8046</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>22.5288</v>
+        <v>22.3972</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.23</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6333</v>
+        <v>0.6353</v>
       </c>
       <c r="J108" t="n">
-        <v>17.7324</v>
+        <v>17.7884</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5524</v>
+        <v>0.5634</v>
       </c>
       <c r="J109" t="n">
-        <v>15.4672</v>
+        <v>15.7752</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.11</v>
       </c>
       <c r="I110" t="n">
-        <v>0.277</v>
+        <v>0.3354</v>
       </c>
       <c r="J110" t="n">
-        <v>7.756</v>
+        <v>9.3912</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0931</v>
+        <v>0.1577</v>
       </c>
       <c r="J111" t="n">
-        <v>2.6068</v>
+        <v>4.4156</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.43</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7267</v>
+        <v>0.906</v>
       </c>
       <c r="J112" t="n">
-        <v>18.8942</v>
+        <v>23.556</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.98</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0029</v>
+        <v>-0.0224</v>
       </c>
       <c r="J113" t="n">
-        <v>0.07539999999999999</v>
+        <v>-0.5824</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.82</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3151</v>
+        <v>-0.204</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.192600000000001</v>
+        <v>-5.304</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5068</v>
+        <v>-0.3306</v>
       </c>
       <c r="J115" t="n">
-        <v>-13.1768</v>
+        <v>-8.595599999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.46</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7947</v>
+        <v>-0.543</v>
       </c>
       <c r="J116" t="n">
-        <v>-20.6622</v>
+        <v>-14.118</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.46</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1391</v>
+        <v>1.0891</v>
       </c>
       <c r="J117" t="n">
-        <v>29.6166</v>
+        <v>28.3166</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7417</v>
+        <v>0.7463</v>
       </c>
       <c r="J118" t="n">
-        <v>19.2842</v>
+        <v>19.4038</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.641</v>
+        <v>0.6532</v>
       </c>
       <c r="J119" t="n">
-        <v>16.666</v>
+        <v>16.9832</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.16</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4033</v>
+        <v>0.4618</v>
       </c>
       <c r="J120" t="n">
-        <v>10.4858</v>
+        <v>12.0068</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5314</v>
+        <v>-0.4615</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.8164</v>
+        <v>-11.999</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8717</v>
+        <v>0.8591</v>
       </c>
       <c r="J122" t="n">
-        <v>26.151</v>
+        <v>25.773</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.27</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7557</v>
+        <v>0.7413</v>
       </c>
       <c r="J123" t="n">
-        <v>22.671</v>
+        <v>22.239</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.23</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6579</v>
+        <v>0.6452</v>
       </c>
       <c r="J124" t="n">
-        <v>19.737</v>
+        <v>19.356</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.12</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3329</v>
+        <v>0.3704</v>
       </c>
       <c r="J125" t="n">
-        <v>9.987</v>
+        <v>11.112</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.76</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8082</v>
+        <v>-0.7624</v>
       </c>
       <c r="J126" t="n">
-        <v>-24.246</v>
+        <v>-22.872</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.17</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3388</v>
+        <v>0.3823</v>
       </c>
       <c r="J127" t="n">
-        <v>10.164</v>
+        <v>11.469</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.08</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1919</v>
+        <v>0.2045</v>
       </c>
       <c r="J128" t="n">
-        <v>5.757</v>
+        <v>6.135</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1735</v>
+        <v>0.1832</v>
       </c>
       <c r="J129" t="n">
-        <v>5.205</v>
+        <v>5.496</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.99</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0417</v>
+        <v>-0.0207</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.251</v>
+        <v>-0.621</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.7</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5206</v>
+        <v>-0.3365</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.618</v>
+        <v>-10.095</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.77</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6984</v>
+        <v>1.4578</v>
       </c>
       <c r="J132" t="n">
-        <v>37.3648</v>
+        <v>32.0716</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.69</v>
       </c>
       <c r="I133" t="n">
-        <v>1.554</v>
+        <v>1.3612</v>
       </c>
       <c r="J133" t="n">
-        <v>34.188</v>
+        <v>29.9464</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1789</v>
+        <v>0.2583</v>
       </c>
       <c r="J134" t="n">
-        <v>3.9358</v>
+        <v>5.6826</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4944</v>
+        <v>-0.4194</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.8768</v>
+        <v>-9.226800000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.88</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5478</v>
+        <v>-0.4763</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.0516</v>
+        <v>-10.4786</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.28</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5778</v>
+        <v>0.6996</v>
       </c>
       <c r="J137" t="n">
-        <v>12.7116</v>
+        <v>15.3912</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.96</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0005</v>
+        <v>-0.032</v>
       </c>
       <c r="J138" t="n">
-        <v>0.011</v>
+        <v>-0.704</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.61</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.589</v>
+        <v>-0.3924</v>
       </c>
       <c r="J139" t="n">
-        <v>-12.958</v>
+        <v>-8.6328</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.55</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6676</v>
+        <v>-0.4484</v>
       </c>
       <c r="J140" t="n">
-        <v>-14.6872</v>
+        <v>-9.864800000000001</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7306</v>
+        <v>-0.4947</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.0732</v>
+        <v>-10.8834</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.03</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1665</v>
+        <v>0.1445</v>
       </c>
       <c r="J142" t="n">
-        <v>4.1625</v>
+        <v>3.6125</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.039</v>
+        <v>-0.0549</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.975</v>
+        <v>-1.3725</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0961</v>
+        <v>-0.0921</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.4025</v>
+        <v>-2.3025</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.67</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.52</v>
+        <v>-0.3424</v>
       </c>
       <c r="J145" t="n">
-        <v>-13</v>
+        <v>-8.56</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.55</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6773</v>
+        <v>-0.4545</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.9325</v>
+        <v>-11.3625</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.74</v>
       </c>
       <c r="I147" t="n">
-        <v>1.6257</v>
+        <v>1.4105</v>
       </c>
       <c r="J147" t="n">
-        <v>40.6425</v>
+        <v>35.2625</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8438</v>
+        <v>0.8799</v>
       </c>
       <c r="J148" t="n">
-        <v>21.095</v>
+        <v>21.9975</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.33</v>
       </c>
       <c r="I149" t="n">
-        <v>0.7946</v>
+        <v>0.8365</v>
       </c>
       <c r="J149" t="n">
-        <v>19.865</v>
+        <v>20.9125</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.21</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4774</v>
+        <v>0.5643</v>
       </c>
       <c r="J150" t="n">
-        <v>11.935</v>
+        <v>14.1075</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.91</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4773</v>
+        <v>-0.3998</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.9325</v>
+        <v>-9.994999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.98</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0618</v>
+        <v>0.0149</v>
       </c>
       <c r="J152" t="n">
-        <v>1.2978</v>
+        <v>0.3129</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0184</v>
+        <v>-0.0217</v>
       </c>
       <c r="J153" t="n">
-        <v>0.3864</v>
+        <v>-0.4557</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4902</v>
+        <v>-0.3301</v>
       </c>
       <c r="J154" t="n">
-        <v>-10.2942</v>
+        <v>-6.9321</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.55</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6575</v>
+        <v>-0.4424</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.8075</v>
+        <v>-9.2904</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6706</v>
+        <v>-0.4517</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.0826</v>
+        <v>-9.4857</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.75</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5902</v>
+        <v>1.3944</v>
       </c>
       <c r="J157" t="n">
-        <v>33.3942</v>
+        <v>29.2824</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.71</v>
       </c>
       <c r="I158" t="n">
-        <v>1.5176</v>
+        <v>1.348</v>
       </c>
       <c r="J158" t="n">
-        <v>31.8696</v>
+        <v>28.308</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.41</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8869</v>
+        <v>0.9802</v>
       </c>
       <c r="J159" t="n">
-        <v>18.6249</v>
+        <v>20.5842</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.19</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3822</v>
+        <v>0.4884</v>
       </c>
       <c r="J160" t="n">
-        <v>8.026199999999999</v>
+        <v>10.2564</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.1</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1548</v>
+        <v>0.2498</v>
       </c>
       <c r="J161" t="n">
-        <v>3.2508</v>
+        <v>5.2458</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3014</v>
+        <v>1.1925</v>
       </c>
       <c r="J162" t="n">
-        <v>32.535</v>
+        <v>29.8125</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.19</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4924</v>
+        <v>0.5366</v>
       </c>
       <c r="J163" t="n">
-        <v>12.31</v>
+        <v>13.415</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.13</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3218</v>
+        <v>0.3847</v>
       </c>
       <c r="J164" t="n">
-        <v>8.045</v>
+        <v>9.6175</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1772</v>
+        <v>0.2448</v>
       </c>
       <c r="J165" t="n">
-        <v>4.43</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1156</v>
+        <v>0.1841</v>
       </c>
       <c r="J166" t="n">
-        <v>2.89</v>
+        <v>4.6025</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.26</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4997</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="J167" t="n">
-        <v>12.4925</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.15</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3427</v>
+        <v>0.3763</v>
       </c>
       <c r="J168" t="n">
-        <v>8.567500000000001</v>
+        <v>9.407500000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3431</v>
+        <v>-0.2179</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.577500000000001</v>
+        <v>-5.4475</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4739</v>
+        <v>-0.3061</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.8475</v>
+        <v>-7.6525</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.6</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.631</v>
+        <v>-0.419</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.775</v>
+        <v>-10.475</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.82</v>
       </c>
       <c r="I172" t="n">
-        <v>1.7819</v>
+        <v>1.5146</v>
       </c>
       <c r="J172" t="n">
-        <v>39.2018</v>
+        <v>33.3212</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.66</v>
       </c>
       <c r="I173" t="n">
-        <v>1.4941</v>
+        <v>1.3222</v>
       </c>
       <c r="J173" t="n">
-        <v>32.8702</v>
+        <v>29.0884</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1167</v>
+        <v>0.1967</v>
       </c>
       <c r="J174" t="n">
-        <v>2.5674</v>
+        <v>4.3274</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0863</v>
+        <v>0.1658</v>
       </c>
       <c r="J175" t="n">
-        <v>1.8986</v>
+        <v>3.6476</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.7685</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.952</v>
+        <v>-16.907</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2128</v>
+        <v>0.2017</v>
       </c>
       <c r="J177" t="n">
-        <v>4.6816</v>
+        <v>4.4374</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0127</v>
+        <v>-0.0387</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.2794</v>
+        <v>-0.8514</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3663</v>
+        <v>-0.245</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.0586</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.429</v>
+        <v>-0.2833</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.438000000000001</v>
+        <v>-6.2326</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.54</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6869</v>
+        <v>-0.4619</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.1118</v>
+        <v>-10.1618</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.13</v>
       </c>
       <c r="I182" t="n">
-        <v>0.323</v>
+        <v>0.2666</v>
       </c>
       <c r="J182" t="n">
-        <v>8.074999999999999</v>
+        <v>6.665</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.86</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2466</v>
+        <v>-0.1638</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.165</v>
+        <v>-4.095</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.83</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2994</v>
+        <v>-0.1942</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.485</v>
+        <v>-4.855</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3479</v>
+        <v>-0.2241</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.6975</v>
+        <v>-5.6025</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.77</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3937</v>
+        <v>-0.2537</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.842499999999999</v>
+        <v>-6.3425</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.53</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.6546</v>
       </c>
       <c r="J187" t="n">
-        <v>18.36</v>
+        <v>16.365</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.3</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4524</v>
+        <v>0.398</v>
       </c>
       <c r="J188" t="n">
-        <v>11.31</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.29</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4387</v>
+        <v>0.3864</v>
       </c>
       <c r="J189" t="n">
-        <v>10.9675</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1168</v>
+        <v>0.1368</v>
       </c>
       <c r="J190" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3791</v>
+        <v>-0.2304</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.477499999999999</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.47</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1506</v>
+        <v>1.0979</v>
       </c>
       <c r="J192" t="n">
-        <v>32.2168</v>
+        <v>30.7412</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.32</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8259</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>23.1252</v>
+        <v>23.3296</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.19</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4742</v>
+        <v>0.5329</v>
       </c>
       <c r="J194" t="n">
-        <v>13.2776</v>
+        <v>14.9212</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.18</v>
       </c>
       <c r="I195" t="n">
-        <v>0.4467</v>
+        <v>0.5084</v>
       </c>
       <c r="J195" t="n">
-        <v>12.5076</v>
+        <v>14.2352</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.95</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3356</v>
+        <v>-0.2559</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.396800000000001</v>
+        <v>-7.1652</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.34</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6077</v>
+        <v>0.7346</v>
       </c>
       <c r="J197" t="n">
-        <v>17.0156</v>
+        <v>20.5688</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0297</v>
+        <v>-0.0402</v>
       </c>
       <c r="J198" t="n">
-        <v>-0.8316</v>
+        <v>-1.1256</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0725</v>
+        <v>-0.0667</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.03</v>
+        <v>-1.8676</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4147</v>
+        <v>-0.2661</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.6116</v>
+        <v>-7.4508</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.47</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.786</v>
+        <v>-0.5363</v>
       </c>
       <c r="J201" t="n">
-        <v>-22.008</v>
+        <v>-15.0164</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.21</v>
       </c>
       <c r="I202" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J202" t="n">
-        <v>41.186</v>
+        <v>36.676</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.94</v>
       </c>
       <c r="I203" t="n">
-        <v>1.863</v>
+        <v>1.5823</v>
       </c>
       <c r="J203" t="n">
-        <v>37.26</v>
+        <v>31.646</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.66</v>
       </c>
       <c r="I204" t="n">
-        <v>1.3617</v>
+        <v>1.2699</v>
       </c>
       <c r="J204" t="n">
-        <v>27.234</v>
+        <v>25.398</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.05</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0188</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.376</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2162</v>
+        <v>-0.1281</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.324</v>
+        <v>-2.562</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.85</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0795</v>
+        <v>-0.0921</v>
       </c>
       <c r="J207" t="n">
-        <v>-1.59</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.79</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.175</v>
+        <v>-0.1641</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.5</v>
+        <v>-3.282</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.53</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.6065</v>
+        <v>-0.4283</v>
       </c>
       <c r="J209" t="n">
-        <v>-12.13</v>
+        <v>-8.566000000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.36</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.8538</v>
+        <v>-0.5899</v>
       </c>
       <c r="J210" t="n">
-        <v>-17.076</v>
+        <v>-11.798</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.24</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.0061</v>
+        <v>-0.7077</v>
       </c>
       <c r="J211" t="n">
-        <v>-20.122</v>
+        <v>-14.154</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.05</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2204</v>
+        <v>0.2105</v>
       </c>
       <c r="J212" t="n">
-        <v>4.8488</v>
+        <v>4.631</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.8</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2934</v>
+        <v>-0.215</v>
       </c>
       <c r="J213" t="n">
-        <v>-6.4548</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3382</v>
+        <v>-0.2335</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.4404</v>
+        <v>-5.137</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.73</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4215</v>
+        <v>-0.2809</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.273</v>
+        <v>-6.1798</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6056</v>
+        <v>-0.4036</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.3232</v>
+        <v>-8.879200000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.49</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1493</v>
+        <v>1.1061</v>
       </c>
       <c r="J217" t="n">
-        <v>25.2846</v>
+        <v>24.3342</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.41</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9805</v>
+        <v>0.9973</v>
       </c>
       <c r="J218" t="n">
-        <v>21.571</v>
+        <v>21.9406</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.34</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8196</v>
+        <v>0.8582</v>
       </c>
       <c r="J219" t="n">
-        <v>18.0312</v>
+        <v>18.8804</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.19</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4274</v>
+        <v>0.5151</v>
       </c>
       <c r="J220" t="n">
-        <v>9.402799999999999</v>
+        <v>11.3322</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.11</v>
       </c>
       <c r="I221" t="n">
-        <v>0.2194</v>
+        <v>0.3053</v>
       </c>
       <c r="J221" t="n">
-        <v>4.8268</v>
+        <v>6.7166</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.78</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.2339</v>
+        <v>-0.2034</v>
       </c>
       <c r="J222" t="n">
-        <v>-4.678</v>
+        <v>-4.068</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.76</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2652</v>
+        <v>-0.2248</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.304</v>
+        <v>-4.496</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.57</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.5891</v>
+        <v>-0.4052</v>
       </c>
       <c r="J224" t="n">
-        <v>-11.782</v>
+        <v>-8.103999999999999</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.5891</v>
+        <v>-0.4052</v>
       </c>
       <c r="J225" t="n">
-        <v>-11.782</v>
+        <v>-8.103999999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.47</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.731</v>
+        <v>-0.4989</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.62</v>
+        <v>-9.978</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.85</v>
       </c>
       <c r="I227" t="n">
-        <v>1.7242</v>
+        <v>1.4885</v>
       </c>
       <c r="J227" t="n">
-        <v>34.484</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.58</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2169</v>
+        <v>1.1826</v>
       </c>
       <c r="J228" t="n">
-        <v>24.338</v>
+        <v>23.652</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.49</v>
       </c>
       <c r="I229" t="n">
-        <v>1.0041</v>
+        <v>1.0796</v>
       </c>
       <c r="J229" t="n">
-        <v>20.082</v>
+        <v>21.592</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.44</v>
       </c>
       <c r="I230" t="n">
-        <v>0.8975</v>
+        <v>1.0148</v>
       </c>
       <c r="J230" t="n">
-        <v>17.95</v>
+        <v>20.296</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.33</v>
       </c>
       <c r="I231" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.7962</v>
       </c>
       <c r="J231" t="n">
-        <v>13.296</v>
+        <v>15.924</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>2.09</v>
       </c>
       <c r="I232" t="n">
-        <v>2.0464</v>
+        <v>1.7644</v>
       </c>
       <c r="J232" t="n">
-        <v>38.8816</v>
+        <v>33.5236</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.53</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1369</v>
+        <v>1.1292</v>
       </c>
       <c r="J233" t="n">
-        <v>21.6011</v>
+        <v>21.4548</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.51</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0918</v>
+        <v>1.106</v>
       </c>
       <c r="J234" t="n">
-        <v>20.7442</v>
+        <v>21.014</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.37</v>
       </c>
       <c r="I235" t="n">
-        <v>0.767</v>
+        <v>0.8928</v>
       </c>
       <c r="J235" t="n">
-        <v>14.573</v>
+        <v>16.9632</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.96</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3682</v>
+        <v>-0.281</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.9958</v>
+        <v>-5.339</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.78</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.206</v>
+        <v>-0.1864</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.914</v>
+        <v>-3.5416</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.76</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.237</v>
+        <v>-0.2087</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.503</v>
+        <v>-3.9653</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.63</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4392</v>
+        <v>-0.3431</v>
       </c>
       <c r="J239" t="n">
-        <v>-8.344799999999999</v>
+        <v>-6.5189</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.4</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.8087</v>
+        <v>-0.5562</v>
       </c>
       <c r="J240" t="n">
-        <v>-15.3653</v>
+        <v>-10.5678</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.33</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8993</v>
+        <v>-0.6238</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.0867</v>
+        <v>-11.8522</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.38</v>
       </c>
       <c r="I242" t="n">
-        <v>1.0253</v>
+        <v>1.0014</v>
       </c>
       <c r="J242" t="n">
-        <v>28.7084</v>
+        <v>28.0392</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.33</v>
       </c>
       <c r="I243" t="n">
-        <v>0.916</v>
+        <v>0.898</v>
       </c>
       <c r="J243" t="n">
-        <v>25.648</v>
+        <v>25.144</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.19</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5806</v>
+        <v>0.5579</v>
       </c>
       <c r="J244" t="n">
-        <v>16.2568</v>
+        <v>15.6212</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.82</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6536</v>
+        <v>-0.5975</v>
       </c>
       <c r="J245" t="n">
-        <v>-18.3008</v>
+        <v>-16.73</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.78</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.7013</v>
       </c>
       <c r="J246" t="n">
-        <v>-21.014</v>
+        <v>-19.6364</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.19</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3797</v>
+        <v>0.4302</v>
       </c>
       <c r="J247" t="n">
-        <v>10.6316</v>
+        <v>12.0456</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.17</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3502</v>
+        <v>0.3925</v>
       </c>
       <c r="J248" t="n">
-        <v>9.8056</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>0.057</v>
+        <v>0.0427</v>
       </c>
       <c r="J249" t="n">
-        <v>1.596</v>
+        <v>1.1956</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4193</v>
+        <v>-0.2652</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.7404</v>
+        <v>-7.4256</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.71</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5014</v>
+        <v>-0.3233</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.0392</v>
+        <v>-9.0524</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.47</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7338</v>
+        <v>0.9106</v>
       </c>
       <c r="J252" t="n">
-        <v>22.014</v>
+        <v>27.318</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.23</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4309</v>
+        <v>0.4982</v>
       </c>
       <c r="J253" t="n">
-        <v>12.927</v>
+        <v>14.946</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.05</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1415</v>
+        <v>0.1422</v>
       </c>
       <c r="J254" t="n">
-        <v>4.245</v>
+        <v>4.266</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.3441</v>
       </c>
       <c r="J255" t="n">
-        <v>-15.921</v>
+        <v>-10.323</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.49</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7737000000000001</v>
+        <v>-0.527</v>
       </c>
       <c r="J256" t="n">
-        <v>-23.211</v>
+        <v>-15.81</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.49</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2365</v>
+        <v>1.1466</v>
       </c>
       <c r="J257" t="n">
-        <v>37.095</v>
+        <v>34.398</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.27</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7603</v>
+        <v>0.7439</v>
       </c>
       <c r="J258" t="n">
-        <v>22.809</v>
+        <v>22.317</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.08</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2138</v>
+        <v>0.2608</v>
       </c>
       <c r="J259" t="n">
-        <v>6.414</v>
+        <v>7.824</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.96</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2704</v>
+        <v>-0.1994</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.112</v>
+        <v>-5.982</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.86</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5622</v>
+        <v>-0.4986</v>
       </c>
       <c r="J261" t="n">
-        <v>-16.866</v>
+        <v>-14.958</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.19</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3919</v>
+        <v>0.4427</v>
       </c>
       <c r="J262" t="n">
-        <v>10.5813</v>
+        <v>11.9529</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.03</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1208</v>
+        <v>0.106</v>
       </c>
       <c r="J263" t="n">
-        <v>3.2616</v>
+        <v>2.862</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>0.002</v>
+        <v>-0.015</v>
       </c>
       <c r="J264" t="n">
-        <v>0.054</v>
+        <v>-0.405</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.92</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1647</v>
+        <v>-0.1052</v>
       </c>
       <c r="J265" t="n">
-        <v>-4.4469</v>
+        <v>-2.8404</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.55</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6968</v>
+        <v>-0.468</v>
       </c>
       <c r="J266" t="n">
-        <v>-18.8136</v>
+        <v>-12.636</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.45</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1605</v>
+        <v>1.0968</v>
       </c>
       <c r="J267" t="n">
-        <v>31.3335</v>
+        <v>29.6136</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.22</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6439</v>
+        <v>0.626</v>
       </c>
       <c r="J268" t="n">
-        <v>17.3853</v>
+        <v>16.902</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.09</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2525</v>
+        <v>0.2917</v>
       </c>
       <c r="J269" t="n">
-        <v>6.8175</v>
+        <v>7.8759</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0118</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="J270" t="n">
-        <v>0.3186</v>
+        <v>1.8117</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.83</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.5769</v>
       </c>
       <c r="J271" t="n">
-        <v>-17.1612</v>
+        <v>-15.5763</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0197</v>
+        <v>1.0074</v>
       </c>
       <c r="J272" t="n">
-        <v>29.5713</v>
+        <v>29.2146</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.37</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9548</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="J273" t="n">
-        <v>27.6892</v>
+        <v>27.6109</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>0.9107</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="J274" t="n">
-        <v>26.4103</v>
+        <v>26.3842</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.22</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5966</v>
+        <v>0.6085</v>
       </c>
       <c r="J275" t="n">
-        <v>17.3014</v>
+        <v>17.6465</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.62</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.122</v>
+        <v>-1.1132</v>
       </c>
       <c r="J276" t="n">
-        <v>-32.538</v>
+        <v>-32.2828</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.21</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4084</v>
+        <v>0.4673</v>
       </c>
       <c r="J277" t="n">
-        <v>11.8436</v>
+        <v>13.5517</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.07</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1865</v>
+        <v>0.1908</v>
       </c>
       <c r="J278" t="n">
-        <v>5.4085</v>
+        <v>5.5332</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.04</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1279</v>
+        <v>0.1224</v>
       </c>
       <c r="J279" t="n">
-        <v>3.7091</v>
+        <v>3.5496</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3616</v>
+        <v>-0.2254</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.4864</v>
+        <v>-6.5366</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.72</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.488</v>
+        <v>-0.3137</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.152</v>
+        <v>-9.097300000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.52</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2769</v>
+        <v>1.1749</v>
       </c>
       <c r="J282" t="n">
-        <v>34.4763</v>
+        <v>31.7223</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.19</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5407</v>
       </c>
       <c r="J283" t="n">
-        <v>14.3289</v>
+        <v>14.5989</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.12</v>
       </c>
       <c r="I284" t="n">
-        <v>0.311</v>
+        <v>0.3644</v>
       </c>
       <c r="J284" t="n">
-        <v>8.397</v>
+        <v>9.838800000000001</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.08</v>
       </c>
       <c r="I285" t="n">
-        <v>0.1919</v>
+        <v>0.252</v>
       </c>
       <c r="J285" t="n">
-        <v>5.1813</v>
+        <v>6.804</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3499</v>
+        <v>-0.275</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.4473</v>
+        <v>-7.425</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>0.8235</v>
+        <v>1.0221</v>
       </c>
       <c r="J287" t="n">
-        <v>22.2345</v>
+        <v>27.5967</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.93</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1332</v>
+        <v>-0.0936</v>
       </c>
       <c r="J288" t="n">
-        <v>-3.5964</v>
+        <v>-2.5272</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2866</v>
+        <v>-0.1795</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.7382</v>
+        <v>-4.8465</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.67</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.5455</v>
+        <v>-0.3561</v>
       </c>
       <c r="J290" t="n">
-        <v>-14.7285</v>
+        <v>-9.614699999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.66</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5585</v>
+        <v>-0.3655</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.0795</v>
+        <v>-9.868499999999999</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.84</v>
       </c>
       <c r="I292" t="n">
-        <v>1.7685</v>
+        <v>1.5085</v>
       </c>
       <c r="J292" t="n">
-        <v>35.37</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.45</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0248</v>
+        <v>1.0442</v>
       </c>
       <c r="J293" t="n">
-        <v>20.496</v>
+        <v>20.884</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.34</v>
       </c>
       <c r="I294" t="n">
-        <v>0.7499</v>
+        <v>0.8472</v>
       </c>
       <c r="J294" t="n">
-        <v>14.998</v>
+        <v>16.944</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3481</v>
+        <v>0.4476</v>
       </c>
       <c r="J295" t="n">
-        <v>6.962</v>
+        <v>8.952</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.13</v>
       </c>
       <c r="I296" t="n">
-        <v>0.247</v>
+        <v>0.3427</v>
       </c>
       <c r="J296" t="n">
-        <v>4.94</v>
+        <v>6.854</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.83</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.2081</v>
+        <v>-0.1756</v>
       </c>
       <c r="J297" t="n">
-        <v>-4.162</v>
+        <v>-3.512</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.83</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2081</v>
+        <v>-0.1756</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.162</v>
+        <v>-3.512</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.78</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2905</v>
+        <v>-0.227</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.81</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.65</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5174</v>
+        <v>-0.3479</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.348</v>
+        <v>-6.958</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.58</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6158</v>
+        <v>-0.4134</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.316</v>
+        <v>-8.268000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.66</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5071</v>
+        <v>1.3294</v>
       </c>
       <c r="J302" t="n">
-        <v>36.1704</v>
+        <v>31.9056</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.27</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6863</v>
+        <v>0.7139</v>
       </c>
       <c r="J303" t="n">
-        <v>16.4712</v>
+        <v>17.1336</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.19</v>
       </c>
       <c r="I304" t="n">
-        <v>0.4575</v>
+        <v>0.5279</v>
       </c>
       <c r="J304" t="n">
-        <v>10.98</v>
+        <v>12.6696</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.13</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2977</v>
+        <v>0.3738</v>
       </c>
       <c r="J305" t="n">
-        <v>7.1448</v>
+        <v>8.9712</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.99</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1981</v>
+        <v>-0.1154</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.7544</v>
+        <v>-2.7696</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.31</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.7347</v>
       </c>
       <c r="J307" t="n">
-        <v>14.5032</v>
+        <v>17.6328</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.83</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2497</v>
+        <v>-0.1877</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.9928</v>
+        <v>-4.5048</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.78</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3496</v>
+        <v>-0.2354</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.3904</v>
+        <v>-5.6496</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.58</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.6361</v>
+        <v>-0.4248</v>
       </c>
       <c r="J310" t="n">
-        <v>-15.2664</v>
+        <v>-10.1952</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.55</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6744</v>
+        <v>-0.4526</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.1856</v>
+        <v>-10.8624</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3649/event_3649_evp_summary.xlsx
+++ b/database/event/3649/event_3649_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.156599999999999</v>
+        <v>9.4079</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2815</v>
+        <v>2.3441</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4957</v>
+        <v>3.6585</v>
       </c>
       <c r="E2" t="n">
-        <v>9.156599999999999</v>
+        <v>9.4079</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4302</v>
+        <v>3.405</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7264</v>
+        <v>6.0029</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5996</v>
+        <v>6.3403</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4315</v>
+        <v>3.4237</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7264</v>
+        <v>6.0029</v>
       </c>
       <c r="K2" t="n">
         <v>91</v>
@@ -529,7 +529,7 @@
         <v>203</v>
       </c>
       <c r="M2" t="n">
-        <v>9.1579</v>
+        <v>9.426600000000001</v>
       </c>
       <c r="N2" t="n">
         <v>294</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.116</v>
+        <v>8.4359</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0222</v>
+        <v>2.1019</v>
       </c>
       <c r="D3" t="n">
-        <v>3.026</v>
+        <v>3.216</v>
       </c>
       <c r="E3" t="n">
-        <v>8.116</v>
+        <v>8.4359</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5163</v>
+        <v>3.4852</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5997</v>
+        <v>4.9507</v>
       </c>
       <c r="H3" t="n">
-        <v>6.9029</v>
+        <v>6.6047</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5892</v>
+        <v>3.5665</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5997</v>
+        <v>4.9507</v>
       </c>
       <c r="K3" t="n">
         <v>91</v>
@@ -575,7 +575,7 @@
         <v>203</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1889</v>
+        <v>8.517200000000001</v>
       </c>
       <c r="N3" t="n">
         <v>294</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.7754</v>
+        <v>6.8183</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6882</v>
+        <v>1.6988</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4207</v>
+        <v>2.4796</v>
       </c>
       <c r="E4" t="n">
-        <v>6.7754</v>
+        <v>6.8183</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5414</v>
+        <v>3.4585</v>
       </c>
       <c r="G4" t="n">
-        <v>3.234</v>
+        <v>3.3598</v>
       </c>
       <c r="H4" t="n">
-        <v>6.9914</v>
+        <v>6.5166</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6352</v>
+        <v>3.5189</v>
       </c>
       <c r="J4" t="n">
-        <v>3.234</v>
+        <v>3.3598</v>
       </c>
       <c r="K4" t="n">
         <v>93</v>
@@ -621,7 +621,7 @@
         <v>182</v>
       </c>
       <c r="M4" t="n">
-        <v>6.8692</v>
+        <v>6.8787</v>
       </c>
       <c r="N4" t="n">
         <v>275</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7155</v>
+        <v>5.8133</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4241</v>
+        <v>1.4484</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9422</v>
+        <v>2.0221</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7155</v>
+        <v>5.8133</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1567</v>
+        <v>3.0914</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5588</v>
+        <v>2.7219</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6359</v>
+        <v>5.3055</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9304</v>
+        <v>2.8649</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5588</v>
+        <v>2.7219</v>
       </c>
       <c r="K5" t="n">
         <v>91</v>
@@ -667,7 +667,7 @@
         <v>203</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4892</v>
+        <v>5.5868</v>
       </c>
       <c r="N5" t="n">
         <v>294</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0201</v>
+        <v>5.0618</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2508</v>
+        <v>1.2612</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6283</v>
+        <v>1.68</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0201</v>
+        <v>5.0618</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0796</v>
+        <v>4.0362</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9405</v>
+        <v>1.0256</v>
       </c>
       <c r="H6" t="n">
-        <v>8.887499999999999</v>
+        <v>8.422700000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6211</v>
+        <v>4.5482</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9405</v>
+        <v>1.0256</v>
       </c>
       <c r="K6" t="n">
         <v>93</v>
@@ -713,7 +713,7 @@
         <v>182</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5616</v>
+        <v>5.573799999999999</v>
       </c>
       <c r="N6" t="n">
         <v>275</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5026</v>
+        <v>4.4839</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1219</v>
+        <v>1.1172</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3947</v>
+        <v>1.417</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5026</v>
+        <v>4.4839</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0492</v>
+        <v>2.0187</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4534</v>
+        <v>2.4652</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0492</v>
+        <v>2.0187</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0655</v>
+        <v>1.0901</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4534</v>
+        <v>2.4652</v>
       </c>
       <c r="K7" t="n">
         <v>91</v>
@@ -759,7 +759,7 @@
         <v>203</v>
       </c>
       <c r="M7" t="n">
-        <v>3.518899999999999</v>
+        <v>3.5553</v>
       </c>
       <c r="N7" t="n">
         <v>294</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3195</v>
+        <v>4.2665</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0762</v>
+        <v>1.063</v>
       </c>
       <c r="D8" t="n">
-        <v>1.312</v>
+        <v>1.318</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3195</v>
+        <v>4.2665</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0251</v>
+        <v>3.934</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2944</v>
+        <v>0.3325</v>
       </c>
       <c r="H8" t="n">
-        <v>8.695600000000001</v>
+        <v>8.085699999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5213</v>
+        <v>4.3662</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2944</v>
+        <v>0.3325</v>
       </c>
       <c r="K8" t="n">
         <v>93</v>
@@ -805,7 +805,7 @@
         <v>182</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8157</v>
+        <v>4.698700000000001</v>
       </c>
       <c r="N8" t="n">
         <v>275</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.0652</v>
+        <v>3.9577</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0129</v>
+        <v>0.9861</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1972</v>
+        <v>1.1774</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0652</v>
+        <v>3.9577</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1961</v>
+        <v>4.1172</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1309</v>
+        <v>-0.1595</v>
       </c>
       <c r="H9" t="n">
-        <v>9.2981</v>
+        <v>8.6899</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8346</v>
+        <v>4.6925</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1309</v>
+        <v>-0.1595</v>
       </c>
       <c r="K9" t="n">
         <v>150</v>
@@ -851,7 +851,7 @@
         <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>4.7037</v>
+        <v>4.532999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>201</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0382</v>
+        <v>2.9366</v>
       </c>
       <c r="C10" t="n">
-        <v>0.757</v>
+        <v>0.7317</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7336</v>
+        <v>0.7126</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0382</v>
+        <v>2.9366</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4304</v>
+        <v>3.3044</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3922</v>
+        <v>-0.3678</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6002</v>
+        <v>6.0082</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4318</v>
+        <v>3.2444</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3922</v>
+        <v>-0.3678</v>
       </c>
       <c r="K10" t="n">
         <v>157</v>
@@ -897,7 +897,7 @@
         <v>72</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0396</v>
+        <v>2.8766</v>
       </c>
       <c r="N10" t="n">
         <v>229</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9932</v>
+        <v>2.9041</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7458</v>
+        <v>0.7236</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7133</v>
+        <v>0.6978</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9932</v>
+        <v>2.9041</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9932</v>
+        <v>3.4622</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.5581</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2127</v>
+        <v>6.5288</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2127</v>
+        <v>3.5255</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.5581</v>
       </c>
       <c r="K11" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2127</v>
+        <v>2.9674</v>
       </c>
       <c r="N11" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9799</v>
+        <v>2.6517</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7425</v>
+        <v>0.6607</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7073</v>
+        <v>0.5829</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9799</v>
+        <v>2.6517</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5039</v>
+        <v>2.6517</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.524</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6.8593</v>
+        <v>3.0788</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5665</v>
+        <v>3.0788</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.524</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0425</v>
+        <v>3.0788</v>
       </c>
       <c r="N12" t="n">
-        <v>201</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8783</v>
+        <v>2.5369</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.6321</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6614</v>
+        <v>0.5306</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8783</v>
+        <v>2.5369</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8783</v>
+        <v>2.5369</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9605</v>
+        <v>2.8276</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9605</v>
+        <v>2.8276</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9605</v>
+        <v>2.8276</v>
       </c>
       <c r="N13" t="n">
         <v>184</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6408</v>
+        <v>2.5268</v>
       </c>
       <c r="C14" t="n">
-        <v>0.658</v>
+        <v>0.6296</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5542</v>
+        <v>0.526</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6408</v>
+        <v>2.5268</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6921</v>
+        <v>2.606</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0513</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>3.999</v>
+        <v>3.7039</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0793</v>
+        <v>2.0001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0513</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>150</v>
@@ -1081,7 +1081,7 @@
         <v>51</v>
       </c>
       <c r="M14" t="n">
-        <v>2.028</v>
+        <v>1.9209</v>
       </c>
       <c r="N14" t="n">
         <v>201</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.539</v>
+        <v>2.4152</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6018</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5082</v>
+        <v>0.4752</v>
       </c>
       <c r="E15" t="n">
-        <v>2.539</v>
+        <v>2.4152</v>
       </c>
       <c r="F15" t="n">
-        <v>2.539</v>
+        <v>2.4152</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.539</v>
+        <v>2.5611</v>
       </c>
       <c r="I15" t="n">
-        <v>2.539</v>
+        <v>2.5611</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.539</v>
+        <v>2.5611</v>
       </c>
       <c r="N15" t="n">
         <v>184</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5247</v>
+        <v>2.3695</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6291</v>
+        <v>0.5904</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5018</v>
+        <v>0.4544</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5247</v>
+        <v>2.3695</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5247</v>
+        <v>2.8081</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.4386</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5247</v>
+        <v>4.3708</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5247</v>
+        <v>2.3602</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.4386</v>
       </c>
       <c r="K16" t="n">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5247</v>
+        <v>1.9216</v>
       </c>
       <c r="N16" t="n">
-        <v>184</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.509</v>
+        <v>2.3488</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6251</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4947</v>
+        <v>0.445</v>
       </c>
       <c r="E17" t="n">
-        <v>2.509</v>
+        <v>2.3488</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9052</v>
+        <v>2.3488</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3962</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7498</v>
+        <v>2.4158</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4697</v>
+        <v>2.4158</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3962</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="L17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0735</v>
+        <v>2.4158</v>
       </c>
       <c r="N17" t="n">
-        <v>229</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2373</v>
+        <v>2.1236</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5574</v>
+        <v>0.5291</v>
       </c>
       <c r="D18" t="n">
-        <v>0.372</v>
+        <v>0.3425</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2373</v>
+        <v>2.1236</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9944</v>
+        <v>2.8966</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7571</v>
+        <v>-0.773</v>
       </c>
       <c r="H18" t="n">
-        <v>5.0641</v>
+        <v>4.6628</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6331</v>
+        <v>2.5179</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7571</v>
+        <v>-0.773</v>
       </c>
       <c r="K18" t="n">
         <v>150</v>
@@ -1265,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.876</v>
+        <v>1.7449</v>
       </c>
       <c r="N18" t="n">
         <v>201</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9715</v>
+        <v>1.8716</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4912</v>
+        <v>0.4663</v>
       </c>
       <c r="D19" t="n">
-        <v>0.252</v>
+        <v>0.2278</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9715</v>
+        <v>1.8716</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2915</v>
+        <v>1.1832</v>
       </c>
       <c r="G19" t="n">
-        <v>0.68</v>
+        <v>0.6884</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2915</v>
+        <v>1.1832</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6715</v>
+        <v>0.6389</v>
       </c>
       <c r="J19" t="n">
-        <v>0.68</v>
+        <v>0.6884</v>
       </c>
       <c r="K19" t="n">
         <v>157</v>
@@ -1311,7 +1311,7 @@
         <v>72</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3515</v>
+        <v>1.3273</v>
       </c>
       <c r="N19" t="n">
         <v>229</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2498</v>
+        <v>1.3944</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3114</v>
+        <v>0.3474</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0738</v>
+        <v>0.0106</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2498</v>
+        <v>1.3944</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8784</v>
+        <v>1.8271</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6286</v>
+        <v>-0.4327</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8784</v>
+        <v>1.8271</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9767</v>
+        <v>0.9866</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6286</v>
+        <v>-0.4327</v>
       </c>
       <c r="K20" t="n">
         <v>91</v>
@@ -1357,7 +1357,7 @@
         <v>203</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3481</v>
+        <v>0.5539000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>294</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.172</v>
+        <v>1.0605</v>
       </c>
       <c r="C21" t="n">
-        <v>0.292</v>
+        <v>0.2642</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1089</v>
+        <v>-0.1414</v>
       </c>
       <c r="E21" t="n">
-        <v>1.172</v>
+        <v>1.0605</v>
       </c>
       <c r="F21" t="n">
-        <v>1.172</v>
+        <v>1.0605</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.172</v>
+        <v>1.0605</v>
       </c>
       <c r="I21" t="n">
-        <v>1.172</v>
+        <v>1.0605</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.172</v>
+        <v>1.0605</v>
       </c>
       <c r="N21" t="n">
         <v>155</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9579</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2387</v>
+        <v>0.2124</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2056</v>
+        <v>-0.2362</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9579</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0274</v>
+        <v>0.9459</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0936</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0274</v>
+        <v>0.9459</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5342</v>
+        <v>0.5108</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0936</v>
       </c>
       <c r="K22" t="n">
         <v>150</v>
@@ -1449,7 +1449,7 @@
         <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4647</v>
+        <v>0.4172</v>
       </c>
       <c r="N22" t="n">
         <v>201</v>
@@ -1458,78 +1458,78 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7029</v>
+        <v>0.6694</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1751</v>
+        <v>0.1668</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3207</v>
+        <v>-0.3195</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7029</v>
+        <v>0.6694</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7029</v>
+        <v>0.377</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.2924</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7029</v>
+        <v>0.377</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7029</v>
+        <v>0.2036</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.2924</v>
       </c>
       <c r="K23" t="n">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7029</v>
+        <v>0.496</v>
       </c>
       <c r="N23" t="n">
-        <v>155</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5401</v>
+        <v>0.6289</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1346</v>
+        <v>0.1567</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3942</v>
+        <v>-0.3379</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5401</v>
+        <v>0.6289</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5401</v>
+        <v>0.6289</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5401</v>
+        <v>0.6289</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5401</v>
+        <v>0.6289</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5401</v>
+        <v>0.6289</v>
       </c>
       <c r="N24" t="n">
         <v>155</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4876</v>
+        <v>0.4452</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1215</v>
+        <v>0.1109</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4179</v>
+        <v>-0.4215</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4876</v>
+        <v>0.4452</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4876</v>
+        <v>0.4452</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4876</v>
+        <v>0.4452</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4876</v>
+        <v>0.4452</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4876</v>
+        <v>0.4452</v>
       </c>
       <c r="N25" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4566</v>
+        <v>0.4269</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1138</v>
+        <v>0.1064</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4319</v>
+        <v>-0.4299</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4566</v>
+        <v>0.4269</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2835</v>
+        <v>0.4269</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1731</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2835</v>
+        <v>0.4269</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1474</v>
+        <v>0.4269</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1731</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="L26" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3205</v>
+        <v>0.4269</v>
       </c>
       <c r="N26" t="n">
-        <v>275</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3887</v>
+        <v>0.3238</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0968</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4625</v>
+        <v>-0.4768</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3887</v>
+        <v>0.3238</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3887</v>
+        <v>0.3238</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3887</v>
+        <v>0.3238</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3887</v>
+        <v>0.3238</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3887</v>
+        <v>0.3238</v>
       </c>
       <c r="N27" t="n">
         <v>120</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3644</v>
+        <v>0.2675</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0667</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4735</v>
+        <v>-0.5024</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3644</v>
+        <v>0.2675</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3644</v>
+        <v>0.2675</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3644</v>
+        <v>0.2675</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3644</v>
+        <v>0.2675</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3644</v>
+        <v>0.2675</v>
       </c>
       <c r="N28" t="n">
         <v>86</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1548</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0386</v>
+        <v>-0.0166</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7079</v>
+        <v>-0.6545</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1548</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1484</v>
+        <v>1.1745</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.3032</v>
+        <v>-1.2411</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1484</v>
+        <v>1.1745</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5971</v>
+        <v>0.6342</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.3032</v>
+        <v>-1.2411</v>
       </c>
       <c r="K29" t="n">
         <v>93</v>
@@ -1771,7 +1771,7 @@
         <v>182</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.6069000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>275</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2256</v>
+        <v>-0.2696</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0562</v>
+        <v>-0.0672</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7399</v>
+        <v>-0.7469</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2256</v>
+        <v>-0.2696</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2256</v>
+        <v>-0.2696</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2256</v>
+        <v>-0.2696</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2256</v>
+        <v>-0.2696</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2256</v>
+        <v>-0.2696</v>
       </c>
       <c r="N30" t="n">
         <v>184</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3667</v>
+        <v>-0.4296</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0914</v>
+        <v>-0.107</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8036</v>
+        <v>-0.8198</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3667</v>
+        <v>-0.4296</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3667</v>
+        <v>-0.4296</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3667</v>
+        <v>-0.4296</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3667</v>
+        <v>-0.4296</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3667</v>
+        <v>-0.4296</v>
       </c>
       <c r="N31" t="n">
         <v>120</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4768</v>
+        <v>-0.5028</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1188</v>
+        <v>-0.1253</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-0.8531</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4768</v>
+        <v>-0.5028</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.065</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4118</v>
+        <v>-0.4304</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.065</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0338</v>
+        <v>-0.0391</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4118</v>
+        <v>-0.4304</v>
       </c>
       <c r="K32" t="n">
         <v>157</v>
@@ -1909,7 +1909,7 @@
         <v>72</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4456</v>
+        <v>-0.4695</v>
       </c>
       <c r="N32" t="n">
         <v>229</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1717</v>
+        <v>-0.178</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.9493</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>184</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8786</v>
+        <v>-0.9048</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2189</v>
+        <v>-0.2254</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0347</v>
+        <v>-1.0361</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8786</v>
+        <v>-0.9048</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8786</v>
+        <v>-0.9048</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8786</v>
+        <v>-0.9048</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8786</v>
+        <v>-0.9048</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8786</v>
+        <v>-0.9048</v>
       </c>
       <c r="N34" t="n">
         <v>120</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0847</v>
+        <v>-1.1617</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2703</v>
+        <v>-0.2894</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1277</v>
+        <v>-1.153</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0847</v>
+        <v>-1.1617</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0847</v>
+        <v>-1.1617</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0847</v>
+        <v>-1.1617</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0847</v>
+        <v>-1.1617</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0847</v>
+        <v>-1.1617</v>
       </c>
       <c r="N35" t="n">
         <v>86</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2588</v>
+        <v>-1.3306</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3136</v>
+        <v>-0.3315</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2063</v>
+        <v>-1.2299</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2588</v>
+        <v>-1.3306</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2588</v>
+        <v>-1.3306</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2588</v>
+        <v>-1.3306</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2588</v>
+        <v>-1.3306</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2588</v>
+        <v>-1.3306</v>
       </c>
       <c r="N36" t="n">
         <v>86</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2712</v>
+        <v>-1.3412</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3167</v>
+        <v>-0.3342</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2119</v>
+        <v>-1.2347</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2712</v>
+        <v>-1.3412</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2712</v>
+        <v>-1.3412</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2712</v>
+        <v>-1.3412</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2712</v>
+        <v>-1.3412</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2712</v>
+        <v>-1.3412</v>
       </c>
       <c r="N37" t="n">
         <v>86</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.315</v>
+        <v>-1.3788</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3276</v>
+        <v>-0.3435</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2317</v>
+        <v>-1.2519</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.315</v>
+        <v>-1.3788</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.315</v>
+        <v>-1.3788</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.315</v>
+        <v>-1.3788</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.315</v>
+        <v>-1.3788</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.315</v>
+        <v>-1.3788</v>
       </c>
       <c r="N38" t="n">
         <v>86</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7858</v>
+        <v>-1.7809</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4449</v>
+        <v>-0.4437</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4442</v>
+        <v>-1.4349</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7858</v>
+        <v>-1.7809</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2136</v>
+        <v>-1.1826</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5722</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2136</v>
+        <v>-1.1826</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.631</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5722</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="K39" t="n">
         <v>157</v>
@@ -2231,7 +2231,7 @@
         <v>72</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2032</v>
+        <v>-1.2369</v>
       </c>
       <c r="N39" t="n">
         <v>229</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8795</v>
+        <v>-1.901</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4683</v>
+        <v>-0.4737</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4865</v>
+        <v>-1.4896</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8795</v>
+        <v>-1.901</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8795</v>
+        <v>-1.901</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8795</v>
+        <v>-1.901</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.8795</v>
+        <v>-1.901</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8795</v>
+        <v>-1.901</v>
       </c>
       <c r="N40" t="n">
         <v>120</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2699</v>
+        <v>-2.2075</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5656</v>
+        <v>-0.55</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6628</v>
+        <v>-1.6291</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2699</v>
+        <v>-2.2075</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2699</v>
+        <v>-2.2075</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2699</v>
+        <v>-2.2075</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2699</v>
+        <v>-2.2075</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2699</v>
+        <v>-2.2075</v>
       </c>
       <c r="N41" t="n">
         <v>155</v>
@@ -2429,10 +2429,10 @@
         <v>1.55</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1703</v>
+        <v>1.1904</v>
       </c>
       <c r="J2" t="n">
-        <v>25.7466</v>
+        <v>26.1888</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.54</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1582</v>
+        <v>1.1727</v>
       </c>
       <c r="J3" t="n">
-        <v>25.4804</v>
+        <v>25.7994</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9706</v>
+        <v>0.9203</v>
       </c>
       <c r="J4" t="n">
-        <v>21.3532</v>
+        <v>20.2466</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.26</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6514</v>
       </c>
       <c r="J5" t="n">
-        <v>14.7818</v>
+        <v>14.3308</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1461</v>
+        <v>0.1731</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2142</v>
+        <v>3.8082</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1681</v>
+        <v>0.1557</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6982</v>
+        <v>3.4254</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1401</v>
+        <v>0.1274</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0822</v>
+        <v>2.8028</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2597</v>
+        <v>-0.2787</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.7134</v>
+        <v>-6.1314</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.61</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3915</v>
+        <v>-0.406</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.613</v>
+        <v>-8.932</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.46</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5308</v>
+        <v>-0.5374</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.6776</v>
+        <v>-11.8228</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1519</v>
+        <v>0.1586</v>
       </c>
       <c r="J12" t="n">
-        <v>4.557</v>
+        <v>4.758</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1172</v>
+        <v>0.1237</v>
       </c>
       <c r="J13" t="n">
-        <v>3.516</v>
+        <v>3.711</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1172</v>
+        <v>0.1237</v>
       </c>
       <c r="J14" t="n">
-        <v>3.516</v>
+        <v>3.711</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2018</v>
+        <v>-0.2169</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.054</v>
+        <v>-6.507</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.71</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3199</v>
+        <v>-0.3331</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.597</v>
+        <v>-9.993</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.31</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4165</v>
+        <v>0.4286</v>
       </c>
       <c r="J17" t="n">
-        <v>12.495</v>
+        <v>12.858</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4165</v>
+        <v>0.4286</v>
       </c>
       <c r="J18" t="n">
-        <v>12.495</v>
+        <v>12.858</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3214</v>
+        <v>0.3371</v>
       </c>
       <c r="J19" t="n">
-        <v>9.641999999999999</v>
+        <v>10.113</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.03</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0473</v>
+        <v>0.0608</v>
       </c>
       <c r="J20" t="n">
-        <v>1.419</v>
+        <v>1.824</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.93</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1171</v>
+        <v>-0.1247</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.513</v>
+        <v>-3.741</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.44</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6814</v>
+        <v>0.656</v>
       </c>
       <c r="J22" t="n">
-        <v>19.0792</v>
+        <v>18.368</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2041</v>
+        <v>0.2093</v>
       </c>
       <c r="J23" t="n">
-        <v>5.7148</v>
+        <v>5.8604</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1589</v>
+        <v>-0.174</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.4492</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.68</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3469</v>
+        <v>-0.3595</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.713200000000001</v>
+        <v>-10.066</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4582</v>
+        <v>-0.4661</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.8296</v>
+        <v>-13.0508</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5221</v>
+        <v>0.5283</v>
       </c>
       <c r="J27" t="n">
-        <v>14.6188</v>
+        <v>14.7924</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.21</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2984</v>
+        <v>0.3144</v>
       </c>
       <c r="J28" t="n">
-        <v>8.3552</v>
+        <v>8.8032</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.19</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2737</v>
+        <v>0.2903</v>
       </c>
       <c r="J29" t="n">
-        <v>7.6636</v>
+        <v>8.128399999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1139</v>
+        <v>0.1298</v>
       </c>
       <c r="J30" t="n">
-        <v>3.1892</v>
+        <v>3.6344</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1616</v>
+        <v>-0.171</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.5248</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.72</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3742</v>
+        <v>1.4804</v>
       </c>
       <c r="J32" t="n">
-        <v>34.355</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.59</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2191</v>
+        <v>1.261</v>
       </c>
       <c r="J33" t="n">
-        <v>30.4775</v>
+        <v>31.525</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.29</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7411</v>
+        <v>0.7127</v>
       </c>
       <c r="J34" t="n">
-        <v>18.5275</v>
+        <v>17.8175</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.649</v>
+        <v>0.631</v>
       </c>
       <c r="J35" t="n">
-        <v>16.225</v>
+        <v>15.775</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2878</v>
+        <v>-0.2635</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.195</v>
+        <v>-6.5875</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.92</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0819</v>
+        <v>-0.1007</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.0475</v>
+        <v>-2.5175</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.87</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1398</v>
+        <v>-0.1594</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.495</v>
+        <v>-3.985</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.87</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1398</v>
+        <v>-0.1594</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.495</v>
+        <v>-3.985</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.241</v>
+        <v>-0.2602</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.025</v>
+        <v>-6.505</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.43</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5581</v>
+        <v>-0.5629</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.9525</v>
+        <v>-14.0725</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.64</v>
       </c>
       <c r="I42" t="n">
-        <v>1.309</v>
+        <v>1.3833</v>
       </c>
       <c r="J42" t="n">
-        <v>34.034</v>
+        <v>35.9658</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.51</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1465</v>
+        <v>1.1489</v>
       </c>
       <c r="J43" t="n">
-        <v>29.809</v>
+        <v>29.8714</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.51</v>
       </c>
       <c r="I44" t="n">
-        <v>1.1465</v>
+        <v>1.1489</v>
       </c>
       <c r="J44" t="n">
-        <v>29.809</v>
+        <v>29.8714</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.82</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6306</v>
+        <v>-0.5843</v>
       </c>
       <c r="J45" t="n">
-        <v>-16.3956</v>
+        <v>-15.1918</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9795</v>
+        <v>-0.8917</v>
       </c>
       <c r="J46" t="n">
-        <v>-25.467</v>
+        <v>-23.1842</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.28</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6319</v>
+        <v>0.6022</v>
       </c>
       <c r="J47" t="n">
-        <v>16.4294</v>
+        <v>15.6572</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.01</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0621</v>
       </c>
       <c r="J48" t="n">
-        <v>1.6562</v>
+        <v>1.6146</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.76</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2648</v>
+        <v>-0.2806</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.8848</v>
+        <v>-7.2956</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3226</v>
+        <v>-0.337</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.387600000000001</v>
+        <v>-8.762</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3321</v>
+        <v>-0.3462</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.634600000000001</v>
+        <v>-9.001200000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.53</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9025</v>
+        <v>0.9949</v>
       </c>
       <c r="J52" t="n">
-        <v>20.7575</v>
+        <v>22.8827</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.43</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7743</v>
+        <v>0.8569</v>
       </c>
       <c r="J53" t="n">
-        <v>17.8089</v>
+        <v>19.7087</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5483</v>
+        <v>0.6089</v>
       </c>
       <c r="J54" t="n">
-        <v>12.6109</v>
+        <v>14.0047</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0521</v>
+        <v>-0.036</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.1983</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.85</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5465</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.5695</v>
+        <v>-11.7208</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.08</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2665</v>
+        <v>0.2574</v>
       </c>
       <c r="J57" t="n">
-        <v>6.1295</v>
+        <v>5.9202</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.99</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0076</v>
+        <v>-0.0062</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1748</v>
+        <v>-0.1426</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0123</v>
+        <v>-0.0245</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.2829</v>
+        <v>-0.5635</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.7</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3136</v>
+        <v>-0.33</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.2128</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.36</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6274</v>
+        <v>-0.6267</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.4302</v>
+        <v>-14.4141</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.39</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7327</v>
+        <v>0.8095</v>
       </c>
       <c r="J62" t="n">
-        <v>20.5156</v>
+        <v>22.666</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.23</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5135</v>
+        <v>0.5684</v>
       </c>
       <c r="J63" t="n">
-        <v>14.378</v>
+        <v>15.9152</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4277</v>
+        <v>0.4715</v>
       </c>
       <c r="J64" t="n">
-        <v>11.9756</v>
+        <v>13.202</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.15</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3988</v>
+        <v>0.4355</v>
       </c>
       <c r="J65" t="n">
-        <v>11.1664</v>
+        <v>12.194</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4514</v>
+        <v>-0.4259</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.6392</v>
+        <v>-11.9252</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0589</v>
+        <v>-0.073</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.6492</v>
+        <v>-2.044</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1186</v>
+        <v>-0.135</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.3208</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.89</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1297</v>
+        <v>-0.1463</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.6316</v>
+        <v>-4.0964</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2104</v>
+        <v>-0.2281</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.8912</v>
+        <v>-6.3868</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.68</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.336</v>
+        <v>-0.351</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.407999999999999</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4067</v>
+        <v>1.5363</v>
       </c>
       <c r="J72" t="n">
-        <v>26.7273</v>
+        <v>29.1897</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.5</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8268</v>
+        <v>0.9212</v>
       </c>
       <c r="J73" t="n">
-        <v>15.7092</v>
+        <v>17.5028</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.42</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7316</v>
+        <v>0.8171</v>
       </c>
       <c r="J74" t="n">
-        <v>13.9004</v>
+        <v>15.5249</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.26</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5251</v>
+        <v>0.589</v>
       </c>
       <c r="J75" t="n">
-        <v>9.976900000000001</v>
+        <v>11.191</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.96</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2686</v>
+        <v>-0.2416</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.1034</v>
+        <v>-4.5904</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.05</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2521</v>
+        <v>0.2306</v>
       </c>
       <c r="J77" t="n">
-        <v>4.7899</v>
+        <v>4.3814</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.04</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2262</v>
+        <v>0.2054</v>
       </c>
       <c r="J78" t="n">
-        <v>4.2978</v>
+        <v>3.9026</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.6</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3925</v>
+        <v>-0.4083</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.4575</v>
+        <v>-7.7577</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.59</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4018</v>
+        <v>-0.4172</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.6342</v>
+        <v>-7.9268</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.32</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.653</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.407</v>
+        <v>-12.3823</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.54</v>
+        <v>0.6034</v>
       </c>
       <c r="J82" t="n">
-        <v>16.2</v>
+        <v>18.102</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.21</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3444</v>
+        <v>0.3553</v>
       </c>
       <c r="J83" t="n">
-        <v>10.332</v>
+        <v>10.659</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1329</v>
+        <v>-0.1459</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.987</v>
+        <v>-4.377</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2476</v>
+        <v>-0.2612</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.428</v>
+        <v>-7.836</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.58</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4462</v>
+        <v>-0.4537</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.386</v>
+        <v>-13.611</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3794</v>
+        <v>0.4189</v>
       </c>
       <c r="J87" t="n">
-        <v>11.382</v>
+        <v>12.567</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2205</v>
+        <v>0.2351</v>
       </c>
       <c r="J88" t="n">
-        <v>6.615</v>
+        <v>7.053</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.02</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0407</v>
+        <v>0.0499</v>
       </c>
       <c r="J89" t="n">
-        <v>1.221</v>
+        <v>1.497</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.01</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0203</v>
+        <v>0.0273</v>
       </c>
       <c r="J90" t="n">
-        <v>0.609</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.87</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1742</v>
+        <v>-0.1859</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.226</v>
+        <v>-5.577</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.66</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0629</v>
+        <v>1.166</v>
       </c>
       <c r="J92" t="n">
-        <v>24.4467</v>
+        <v>26.818</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.29</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5878</v>
+        <v>0.6532</v>
       </c>
       <c r="J93" t="n">
-        <v>13.5194</v>
+        <v>15.0236</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.14</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3766</v>
+        <v>0.4063</v>
       </c>
       <c r="J94" t="n">
-        <v>8.661799999999999</v>
+        <v>9.344900000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1138</v>
+        <v>0.134</v>
       </c>
       <c r="J95" t="n">
-        <v>2.6174</v>
+        <v>3.082</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.98</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1502</v>
+        <v>-0.1387</v>
       </c>
       <c r="J96" t="n">
-        <v>-3.4546</v>
+        <v>-3.1901</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3872</v>
+        <v>0.4079</v>
       </c>
       <c r="J97" t="n">
-        <v>8.9056</v>
+        <v>9.3817</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.9</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1186</v>
+        <v>-0.135</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.7278</v>
+        <v>-3.105</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.83</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1907</v>
+        <v>-0.2084</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.3861</v>
+        <v>-4.7932</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2398</v>
+        <v>-0.2572</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.5154</v>
+        <v>-5.9156</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4482</v>
+        <v>-0.4581</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.3086</v>
+        <v>-10.5363</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.46</v>
+        <v>0.4494</v>
       </c>
       <c r="J102" t="n">
-        <v>12.88</v>
+        <v>12.5832</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0104</v>
+        <v>0.0074</v>
       </c>
       <c r="J103" t="n">
-        <v>0.2912</v>
+        <v>0.2072</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.95</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0711</v>
+        <v>-0.0824</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.9908</v>
+        <v>-2.3072</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.79</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2418</v>
+        <v>-0.2567</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.7704</v>
+        <v>-7.1876</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.76</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2714</v>
+        <v>-0.2858</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.5992</v>
+        <v>-8.0024</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7574</v>
       </c>
       <c r="J107" t="n">
-        <v>22.3972</v>
+        <v>21.2072</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.23</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6353</v>
+        <v>0.6118</v>
       </c>
       <c r="J108" t="n">
-        <v>17.7884</v>
+        <v>17.1304</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5634</v>
+        <v>0.5474</v>
       </c>
       <c r="J109" t="n">
-        <v>15.7752</v>
+        <v>15.3272</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.11</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3354</v>
+        <v>0.3394</v>
       </c>
       <c r="J110" t="n">
-        <v>9.3912</v>
+        <v>9.5032</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1577</v>
+        <v>0.1733</v>
       </c>
       <c r="J111" t="n">
-        <v>4.4156</v>
+        <v>4.8524</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.43</v>
       </c>
       <c r="I112" t="n">
-        <v>0.906</v>
+        <v>0.8468</v>
       </c>
       <c r="J112" t="n">
-        <v>23.556</v>
+        <v>22.0168</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.98</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0224</v>
+        <v>-0.0323</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.5824</v>
+        <v>-0.8398</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.82</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.204</v>
+        <v>-0.2208</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.304</v>
+        <v>-5.7408</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3306</v>
+        <v>-0.345</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.595599999999999</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.46</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.543</v>
+        <v>-0.547</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.118</v>
+        <v>-14.222</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.46</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0891</v>
+        <v>1.0469</v>
       </c>
       <c r="J117" t="n">
-        <v>28.3166</v>
+        <v>27.2194</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7463</v>
+        <v>0.7116</v>
       </c>
       <c r="J118" t="n">
-        <v>19.4038</v>
+        <v>18.5016</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6532</v>
+        <v>0.629</v>
       </c>
       <c r="J119" t="n">
-        <v>16.9832</v>
+        <v>16.354</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.16</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4618</v>
+        <v>0.4563</v>
       </c>
       <c r="J120" t="n">
-        <v>12.0068</v>
+        <v>11.8638</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4615</v>
+        <v>-0.433</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.999</v>
+        <v>-11.258</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8591</v>
+        <v>0.8069</v>
       </c>
       <c r="J122" t="n">
-        <v>25.773</v>
+        <v>24.207</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.27</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7413</v>
+        <v>0.7036</v>
       </c>
       <c r="J123" t="n">
-        <v>22.239</v>
+        <v>21.108</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.23</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6452</v>
+        <v>0.6186</v>
       </c>
       <c r="J124" t="n">
-        <v>19.356</v>
+        <v>18.558</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.12</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3704</v>
+        <v>0.3698</v>
       </c>
       <c r="J125" t="n">
-        <v>11.112</v>
+        <v>11.094</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.76</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7624</v>
+        <v>-0.7052</v>
       </c>
       <c r="J126" t="n">
-        <v>-22.872</v>
+        <v>-21.156</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.17</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3823</v>
+        <v>0.3814</v>
       </c>
       <c r="J127" t="n">
-        <v>11.469</v>
+        <v>11.442</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.08</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2045</v>
+        <v>0.2121</v>
       </c>
       <c r="J128" t="n">
-        <v>6.135</v>
+        <v>6.363</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1832</v>
+        <v>0.1913</v>
       </c>
       <c r="J129" t="n">
-        <v>5.496</v>
+        <v>5.739</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.99</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0207</v>
+        <v>-0.0253</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.621</v>
+        <v>-0.759</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.7</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3365</v>
+        <v>-0.3479</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.095</v>
+        <v>-10.437</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.77</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4578</v>
+        <v>1.4433</v>
       </c>
       <c r="J132" t="n">
-        <v>32.0716</v>
+        <v>31.7526</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.69</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3612</v>
+        <v>1.3414</v>
       </c>
       <c r="J133" t="n">
-        <v>29.9464</v>
+        <v>29.5108</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2583</v>
+        <v>0.2729</v>
       </c>
       <c r="J134" t="n">
-        <v>5.6826</v>
+        <v>6.0038</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4194</v>
+        <v>-0.3913</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.226800000000001</v>
+        <v>-8.608599999999999</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.88</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4763</v>
+        <v>-0.4434</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.4786</v>
+        <v>-9.754799999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.28</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6996</v>
+        <v>0.6525</v>
       </c>
       <c r="J137" t="n">
-        <v>15.3912</v>
+        <v>14.355</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.96</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.032</v>
+        <v>-0.0484</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.704</v>
+        <v>-1.0648</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.61</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3924</v>
+        <v>-0.4067</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.6328</v>
+        <v>-8.9474</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.55</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4484</v>
+        <v>-0.4598</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.864800000000001</v>
+        <v>-10.1156</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4947</v>
+        <v>-0.5034</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.8834</v>
+        <v>-11.0748</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.03</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1445</v>
+        <v>0.1383</v>
       </c>
       <c r="J142" t="n">
-        <v>3.6125</v>
+        <v>3.4575</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0549</v>
+        <v>-0.0699</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.3725</v>
+        <v>-1.7475</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0921</v>
+        <v>-0.1087</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.3025</v>
+        <v>-2.7175</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.67</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3424</v>
+        <v>-0.3577</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.56</v>
+        <v>-8.942500000000001</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.55</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4545</v>
+        <v>-0.4646</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.3625</v>
+        <v>-11.615</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.74</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4105</v>
+        <v>1.3953</v>
       </c>
       <c r="J147" t="n">
-        <v>35.2625</v>
+        <v>34.8825</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8799</v>
+        <v>0.8337</v>
       </c>
       <c r="J148" t="n">
-        <v>21.9975</v>
+        <v>20.8425</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.33</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8365</v>
+        <v>0.7955</v>
       </c>
       <c r="J149" t="n">
-        <v>20.9125</v>
+        <v>19.8875</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.21</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5643</v>
+        <v>0.5532</v>
       </c>
       <c r="J150" t="n">
-        <v>14.1075</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.91</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3998</v>
+        <v>-0.3711</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.994999999999999</v>
+        <v>-9.2775</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.98</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0149</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>0.3129</v>
+        <v>-0.1764</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0217</v>
+        <v>-0.0403</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.4557</v>
+        <v>-0.8463000000000001</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3301</v>
+        <v>-0.3481</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.9321</v>
+        <v>-7.3101</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.55</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4424</v>
+        <v>-0.4551</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.2904</v>
+        <v>-9.5571</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4517</v>
+        <v>-0.4639</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.4857</v>
+        <v>-9.741899999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.75</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3944</v>
+        <v>1.3832</v>
       </c>
       <c r="J157" t="n">
-        <v>29.2824</v>
+        <v>29.0472</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.71</v>
       </c>
       <c r="I158" t="n">
-        <v>1.348</v>
+        <v>1.334</v>
       </c>
       <c r="J158" t="n">
-        <v>28.308</v>
+        <v>28.014</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.41</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9802</v>
+        <v>0.9315</v>
       </c>
       <c r="J159" t="n">
-        <v>20.5842</v>
+        <v>19.5615</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.19</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4884</v>
+        <v>0.4905</v>
       </c>
       <c r="J160" t="n">
-        <v>10.2564</v>
+        <v>10.3005</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.1</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2498</v>
+        <v>0.2735</v>
       </c>
       <c r="J161" t="n">
-        <v>5.2458</v>
+        <v>5.7435</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1925</v>
+        <v>1.1589</v>
       </c>
       <c r="J162" t="n">
-        <v>29.8125</v>
+        <v>28.9725</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.19</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5366</v>
+        <v>0.5239</v>
       </c>
       <c r="J163" t="n">
-        <v>13.415</v>
+        <v>13.0975</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.13</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3847</v>
+        <v>0.3858</v>
       </c>
       <c r="J164" t="n">
-        <v>9.6175</v>
+        <v>9.645</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2448</v>
+        <v>0.2567</v>
       </c>
       <c r="J165" t="n">
-        <v>6.12</v>
+        <v>6.4175</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1841</v>
+        <v>0.1997</v>
       </c>
       <c r="J166" t="n">
-        <v>4.6025</v>
+        <v>4.9925</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.26</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5616</v>
       </c>
       <c r="J167" t="n">
-        <v>14.63</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.15</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3763</v>
+        <v>0.3692</v>
       </c>
       <c r="J168" t="n">
-        <v>9.407500000000001</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2179</v>
+        <v>-0.2338</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.4475</v>
+        <v>-5.845</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3061</v>
+        <v>-0.3204</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.6525</v>
+        <v>-8.01</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.6</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.419</v>
+        <v>-0.4291</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.475</v>
+        <v>-10.7275</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.82</v>
       </c>
       <c r="I172" t="n">
-        <v>1.5146</v>
+        <v>1.5035</v>
       </c>
       <c r="J172" t="n">
-        <v>33.3212</v>
+        <v>33.077</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.66</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3222</v>
+        <v>1.3005</v>
       </c>
       <c r="J173" t="n">
-        <v>29.0884</v>
+        <v>28.611</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1967</v>
+        <v>0.216</v>
       </c>
       <c r="J174" t="n">
-        <v>4.3274</v>
+        <v>4.752</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1658</v>
+        <v>0.1869</v>
       </c>
       <c r="J175" t="n">
-        <v>3.6476</v>
+        <v>4.1118</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7685</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.907</v>
+        <v>-15.5122</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2017</v>
+        <v>0.1934</v>
       </c>
       <c r="J177" t="n">
-        <v>4.4374</v>
+        <v>4.2548</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0387</v>
+        <v>-0.0537</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.8514</v>
+        <v>-1.1814</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.245</v>
+        <v>-0.2633</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.39</v>
+        <v>-5.7926</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2833</v>
+        <v>-0.3009</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.2326</v>
+        <v>-6.6198</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.54</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4619</v>
+        <v>-0.4719</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.1618</v>
+        <v>-10.3818</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.13</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2666</v>
+        <v>0.2667</v>
       </c>
       <c r="J182" t="n">
-        <v>6.665</v>
+        <v>6.6675</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.86</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1638</v>
+        <v>-0.1804</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.095</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.83</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1942</v>
+        <v>-0.211</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.855</v>
+        <v>-5.275</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2241</v>
+        <v>-0.2408</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.6025</v>
+        <v>-6.02</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.77</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2537</v>
+        <v>-0.27</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.3425</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.53</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6546</v>
+        <v>0.6542</v>
       </c>
       <c r="J187" t="n">
-        <v>16.365</v>
+        <v>16.355</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.3</v>
       </c>
       <c r="I188" t="n">
-        <v>0.398</v>
+        <v>0.4123</v>
       </c>
       <c r="J188" t="n">
-        <v>9.949999999999999</v>
+        <v>10.3075</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.29</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3864</v>
+        <v>0.4012</v>
       </c>
       <c r="J189" t="n">
-        <v>9.66</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1368</v>
+        <v>0.155</v>
       </c>
       <c r="J190" t="n">
-        <v>3.42</v>
+        <v>3.875</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2304</v>
+        <v>-0.2392</v>
       </c>
       <c r="J191" t="n">
-        <v>-5.76</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.47</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0979</v>
+        <v>1.0578</v>
       </c>
       <c r="J192" t="n">
-        <v>30.7412</v>
+        <v>29.6184</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.32</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.7889</v>
       </c>
       <c r="J193" t="n">
-        <v>23.3296</v>
+        <v>22.0892</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.19</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5329</v>
+        <v>0.5214</v>
       </c>
       <c r="J194" t="n">
-        <v>14.9212</v>
+        <v>14.5992</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.18</v>
       </c>
       <c r="I195" t="n">
-        <v>0.5084</v>
+        <v>0.4992</v>
       </c>
       <c r="J195" t="n">
-        <v>14.2352</v>
+        <v>13.9776</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.95</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2559</v>
+        <v>-0.2411</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.1652</v>
+        <v>-6.7508</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.34</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7346</v>
+        <v>0.6957</v>
       </c>
       <c r="J197" t="n">
-        <v>20.5688</v>
+        <v>19.4796</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0402</v>
+        <v>-0.0508</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.1256</v>
+        <v>-1.4224</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0667</v>
+        <v>-0.0791</v>
       </c>
       <c r="J199" t="n">
-        <v>-1.8676</v>
+        <v>-2.2148</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2661</v>
+        <v>-0.2816</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.4508</v>
+        <v>-7.8848</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.47</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5363</v>
+        <v>-0.5404</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.0164</v>
+        <v>-15.1312</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.21</v>
       </c>
       <c r="I202" t="n">
-        <v>1.8338</v>
+        <v>1.8919</v>
       </c>
       <c r="J202" t="n">
-        <v>36.676</v>
+        <v>37.838</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.94</v>
       </c>
       <c r="I203" t="n">
-        <v>1.5823</v>
+        <v>1.586</v>
       </c>
       <c r="J203" t="n">
-        <v>31.646</v>
+        <v>31.72</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.66</v>
       </c>
       <c r="I204" t="n">
-        <v>1.2699</v>
+        <v>1.2547</v>
       </c>
       <c r="J204" t="n">
-        <v>25.398</v>
+        <v>25.094</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.05</v>
       </c>
       <c r="I205" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.1131</v>
       </c>
       <c r="J205" t="n">
-        <v>1.438</v>
+        <v>2.262</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1281</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.562</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.85</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0921</v>
+        <v>-0.1266</v>
       </c>
       <c r="J207" t="n">
-        <v>-1.842</v>
+        <v>-2.532</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.79</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1641</v>
+        <v>-0.1962</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.282</v>
+        <v>-3.924</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.53</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.4283</v>
+        <v>-0.4472</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.566000000000001</v>
+        <v>-8.944000000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.36</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5899</v>
+        <v>-0.5969</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.798</v>
+        <v>-11.938</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.24</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7077</v>
+        <v>-0.7044</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.154</v>
+        <v>-14.088</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.05</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2105</v>
+        <v>0.1999</v>
       </c>
       <c r="J212" t="n">
-        <v>4.631</v>
+        <v>4.3978</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.8</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.215</v>
+        <v>-0.2339</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.73</v>
+        <v>-5.1458</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2335</v>
+        <v>-0.2524</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.137</v>
+        <v>-5.5528</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.73</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2809</v>
+        <v>-0.299</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.1798</v>
+        <v>-6.578</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4036</v>
+        <v>-0.417</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.879200000000001</v>
+        <v>-9.173999999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.49</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1061</v>
+        <v>1.0705</v>
       </c>
       <c r="J217" t="n">
-        <v>24.3342</v>
+        <v>23.551</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.41</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9973</v>
+        <v>0.9455</v>
       </c>
       <c r="J218" t="n">
-        <v>21.9406</v>
+        <v>20.801</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.34</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8582</v>
+        <v>0.8146</v>
       </c>
       <c r="J219" t="n">
-        <v>18.8804</v>
+        <v>17.9212</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.19</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5151</v>
+        <v>0.5091</v>
       </c>
       <c r="J220" t="n">
-        <v>11.3322</v>
+        <v>11.2002</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.11</v>
       </c>
       <c r="I221" t="n">
-        <v>0.3053</v>
+        <v>0.3186</v>
       </c>
       <c r="J221" t="n">
-        <v>6.7166</v>
+        <v>7.0092</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.78</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.2034</v>
+        <v>-0.2291</v>
       </c>
       <c r="J222" t="n">
-        <v>-4.068</v>
+        <v>-4.582</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.76</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2248</v>
+        <v>-0.2497</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.496</v>
+        <v>-4.994</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.57</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.4052</v>
+        <v>-0.423</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.103999999999999</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4052</v>
+        <v>-0.423</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.103999999999999</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.47</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4989</v>
+        <v>-0.5109</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.978</v>
+        <v>-10.218</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.85</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4885</v>
+        <v>1.4862</v>
       </c>
       <c r="J227" t="n">
-        <v>29.77</v>
+        <v>29.724</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.58</v>
       </c>
       <c r="I228" t="n">
-        <v>1.1826</v>
+        <v>1.1598</v>
       </c>
       <c r="J228" t="n">
-        <v>23.652</v>
+        <v>23.196</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.49</v>
       </c>
       <c r="I229" t="n">
-        <v>1.0796</v>
+        <v>1.0467</v>
       </c>
       <c r="J229" t="n">
-        <v>21.592</v>
+        <v>20.934</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.44</v>
       </c>
       <c r="I230" t="n">
-        <v>1.0148</v>
+        <v>0.9714</v>
       </c>
       <c r="J230" t="n">
-        <v>20.296</v>
+        <v>19.428</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.33</v>
       </c>
       <c r="I231" t="n">
-        <v>0.7962</v>
+        <v>0.7678</v>
       </c>
       <c r="J231" t="n">
-        <v>15.924</v>
+        <v>15.356</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>2.09</v>
       </c>
       <c r="I232" t="n">
-        <v>1.7644</v>
+        <v>1.7736</v>
       </c>
       <c r="J232" t="n">
-        <v>33.5236</v>
+        <v>33.6984</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.53</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1292</v>
+        <v>1.1011</v>
       </c>
       <c r="J233" t="n">
-        <v>21.4548</v>
+        <v>20.9209</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.51</v>
       </c>
       <c r="I234" t="n">
-        <v>1.106</v>
+        <v>1.0757</v>
       </c>
       <c r="J234" t="n">
-        <v>21.014</v>
+        <v>20.4383</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.37</v>
       </c>
       <c r="I235" t="n">
-        <v>0.8928</v>
+        <v>0.851</v>
       </c>
       <c r="J235" t="n">
-        <v>16.9632</v>
+        <v>16.169</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.96</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.281</v>
+        <v>-0.2504</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.339</v>
+        <v>-4.7576</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.78</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1864</v>
+        <v>-0.2157</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.5416</v>
+        <v>-4.0983</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.76</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2087</v>
+        <v>-0.2371</v>
       </c>
       <c r="J238" t="n">
-        <v>-3.9653</v>
+        <v>-4.5049</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.63</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3431</v>
+        <v>-0.3653</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.5189</v>
+        <v>-6.9407</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.4</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5562</v>
+        <v>-0.5653</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.5678</v>
+        <v>-10.7407</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.33</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6238</v>
+        <v>-0.6274</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.8522</v>
+        <v>-11.9206</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.38</v>
       </c>
       <c r="I242" t="n">
-        <v>1.0014</v>
+        <v>0.9383</v>
       </c>
       <c r="J242" t="n">
-        <v>28.0392</v>
+        <v>26.2724</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.33</v>
       </c>
       <c r="I243" t="n">
-        <v>0.898</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="J243" t="n">
-        <v>25.144</v>
+        <v>23.4696</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.19</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5579</v>
+        <v>0.5384</v>
       </c>
       <c r="J244" t="n">
-        <v>15.6212</v>
+        <v>15.0752</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.82</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5975</v>
+        <v>-0.5609</v>
       </c>
       <c r="J245" t="n">
-        <v>-16.73</v>
+        <v>-15.7052</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.78</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7013</v>
+        <v>-0.6532</v>
       </c>
       <c r="J246" t="n">
-        <v>-19.6364</v>
+        <v>-18.2896</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.19</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4302</v>
+        <v>0.4239</v>
       </c>
       <c r="J247" t="n">
-        <v>12.0456</v>
+        <v>11.8692</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.17</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3925</v>
+        <v>0.3888</v>
       </c>
       <c r="J248" t="n">
-        <v>10.99</v>
+        <v>10.8864</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0427</v>
+        <v>0.0469</v>
       </c>
       <c r="J249" t="n">
-        <v>1.1956</v>
+        <v>1.3132</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2652</v>
+        <v>-0.279</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.4256</v>
+        <v>-7.812</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.71</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3233</v>
+        <v>-0.3357</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.0524</v>
+        <v>-9.3996</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.47</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9106</v>
+        <v>0.86</v>
       </c>
       <c r="J252" t="n">
-        <v>27.318</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.23</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4982</v>
+        <v>0.4877</v>
       </c>
       <c r="J253" t="n">
-        <v>14.946</v>
+        <v>14.631</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.05</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1422</v>
+        <v>0.15</v>
       </c>
       <c r="J254" t="n">
-        <v>4.266</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3441</v>
+        <v>-0.3556</v>
       </c>
       <c r="J255" t="n">
-        <v>-10.323</v>
+        <v>-10.668</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.49</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.527</v>
+        <v>-0.5303</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.81</v>
+        <v>-15.909</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.49</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1466</v>
+        <v>1.1064</v>
       </c>
       <c r="J257" t="n">
-        <v>34.398</v>
+        <v>33.192</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.27</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7439</v>
+        <v>0.7055</v>
       </c>
       <c r="J258" t="n">
-        <v>22.317</v>
+        <v>21.165</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.08</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2608</v>
+        <v>0.2677</v>
       </c>
       <c r="J259" t="n">
-        <v>7.824</v>
+        <v>8.031000000000001</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.96</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1994</v>
+        <v>-0.193</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.982</v>
+        <v>-5.79</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.86</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4986</v>
+        <v>-0.4704</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.958</v>
+        <v>-14.112</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.19</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4427</v>
+        <v>0.4331</v>
       </c>
       <c r="J262" t="n">
-        <v>11.9529</v>
+        <v>11.6937</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.03</v>
       </c>
       <c r="I263" t="n">
-        <v>0.106</v>
+        <v>0.1102</v>
       </c>
       <c r="J263" t="n">
-        <v>2.862</v>
+        <v>2.9754</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.015</v>
+        <v>-0.021</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.405</v>
+        <v>-0.5669999999999999</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.92</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1052</v>
+        <v>-0.1187</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.8404</v>
+        <v>-3.2049</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.55</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.468</v>
+        <v>-0.4753</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.636</v>
+        <v>-12.8331</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.45</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0968</v>
+        <v>1.0514</v>
       </c>
       <c r="J267" t="n">
-        <v>29.6136</v>
+        <v>28.3878</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.22</v>
       </c>
       <c r="I268" t="n">
-        <v>0.626</v>
+        <v>0.6005</v>
       </c>
       <c r="J268" t="n">
-        <v>16.902</v>
+        <v>16.2135</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.09</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2917</v>
+        <v>0.296</v>
       </c>
       <c r="J269" t="n">
-        <v>7.8759</v>
+        <v>7.992</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0814</v>
       </c>
       <c r="J270" t="n">
-        <v>1.8117</v>
+        <v>2.1978</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.83</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5769</v>
+        <v>-0.5414</v>
       </c>
       <c r="J271" t="n">
-        <v>-15.5763</v>
+        <v>-14.6178</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0074</v>
+        <v>0.9507</v>
       </c>
       <c r="J272" t="n">
-        <v>29.2146</v>
+        <v>27.5703</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.37</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.8939</v>
       </c>
       <c r="J273" t="n">
-        <v>27.6109</v>
+        <v>25.9231</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8546</v>
       </c>
       <c r="J274" t="n">
-        <v>26.3842</v>
+        <v>24.7834</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.22</v>
       </c>
       <c r="I275" t="n">
-        <v>0.6085</v>
+        <v>0.5885</v>
       </c>
       <c r="J275" t="n">
-        <v>17.6465</v>
+        <v>17.0665</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.62</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.1132</v>
+        <v>-1.0088</v>
       </c>
       <c r="J276" t="n">
-        <v>-32.2828</v>
+        <v>-29.2552</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.21</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4673</v>
+        <v>0.4583</v>
       </c>
       <c r="J277" t="n">
-        <v>13.5517</v>
+        <v>13.2907</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.07</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1908</v>
+        <v>0.1968</v>
       </c>
       <c r="J278" t="n">
-        <v>5.5332</v>
+        <v>5.7072</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.04</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1224</v>
+        <v>0.1291</v>
       </c>
       <c r="J279" t="n">
-        <v>3.5496</v>
+        <v>3.7439</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2254</v>
+        <v>-0.2397</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.5366</v>
+        <v>-6.9513</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.72</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3137</v>
+        <v>-0.3264</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.097300000000001</v>
+        <v>-9.4656</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.52</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1749</v>
+        <v>1.1386</v>
       </c>
       <c r="J282" t="n">
-        <v>31.7223</v>
+        <v>30.7422</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.19</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5407</v>
+        <v>0.5266</v>
       </c>
       <c r="J283" t="n">
-        <v>14.5989</v>
+        <v>14.2182</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.12</v>
       </c>
       <c r="I284" t="n">
-        <v>0.3644</v>
+        <v>0.3657</v>
       </c>
       <c r="J284" t="n">
-        <v>9.838800000000001</v>
+        <v>9.873900000000001</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.08</v>
       </c>
       <c r="I285" t="n">
-        <v>0.252</v>
+        <v>0.2616</v>
       </c>
       <c r="J285" t="n">
-        <v>6.804</v>
+        <v>7.0632</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.275</v>
+        <v>-0.2624</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.425</v>
+        <v>-7.0848</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>1.0221</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="J287" t="n">
-        <v>27.5967</v>
+        <v>26.1711</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.93</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0936</v>
+        <v>-0.1066</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.5272</v>
+        <v>-2.8782</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1795</v>
+        <v>-0.1949</v>
       </c>
       <c r="J289" t="n">
-        <v>-4.8465</v>
+        <v>-5.2623</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.67</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3561</v>
+        <v>-0.3684</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.614699999999999</v>
+        <v>-9.9468</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.66</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3655</v>
+        <v>-0.3775</v>
       </c>
       <c r="J291" t="n">
-        <v>-9.868499999999999</v>
+        <v>-10.1925</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.84</v>
       </c>
       <c r="I292" t="n">
-        <v>1.5085</v>
+        <v>1.5019</v>
       </c>
       <c r="J292" t="n">
-        <v>30.17</v>
+        <v>30.038</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.45</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0442</v>
+        <v>1.0012</v>
       </c>
       <c r="J293" t="n">
-        <v>20.884</v>
+        <v>20.024</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.34</v>
       </c>
       <c r="I294" t="n">
-        <v>0.8472</v>
+        <v>0.8072</v>
       </c>
       <c r="J294" t="n">
-        <v>16.944</v>
+        <v>16.144</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.4476</v>
+        <v>0.4519</v>
       </c>
       <c r="J295" t="n">
-        <v>8.952</v>
+        <v>9.038</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.13</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3427</v>
+        <v>0.3566</v>
       </c>
       <c r="J296" t="n">
-        <v>6.854</v>
+        <v>7.132</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.83</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1756</v>
+        <v>-0.1968</v>
       </c>
       <c r="J297" t="n">
-        <v>-3.512</v>
+        <v>-3.936</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.83</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1756</v>
+        <v>-0.1968</v>
       </c>
       <c r="J298" t="n">
-        <v>-3.512</v>
+        <v>-3.936</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.78</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.227</v>
+        <v>-0.2474</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.54</v>
+        <v>-4.948</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.65</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3479</v>
+        <v>-0.3654</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.958</v>
+        <v>-7.308</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.58</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4134</v>
+        <v>-0.4279</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.268000000000001</v>
+        <v>-8.558</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.66</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3294</v>
+        <v>1.3069</v>
       </c>
       <c r="J302" t="n">
-        <v>31.9056</v>
+        <v>31.3656</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.27</v>
       </c>
       <c r="I303" t="n">
-        <v>0.7139</v>
+        <v>0.6848</v>
       </c>
       <c r="J303" t="n">
-        <v>17.1336</v>
+        <v>16.4352</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.19</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5279</v>
+        <v>0.5179</v>
       </c>
       <c r="J304" t="n">
-        <v>12.6696</v>
+        <v>12.4296</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.13</v>
       </c>
       <c r="I305" t="n">
-        <v>0.3738</v>
+        <v>0.3783</v>
       </c>
       <c r="J305" t="n">
-        <v>8.9712</v>
+        <v>9.0792</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.99</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1154</v>
+        <v>-0.1017</v>
       </c>
       <c r="J306" t="n">
-        <v>-2.7696</v>
+        <v>-2.4408</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.31</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7347</v>
+        <v>0.6874</v>
       </c>
       <c r="J307" t="n">
-        <v>17.6328</v>
+        <v>16.4976</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.83</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1877</v>
+        <v>-0.2061</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.5048</v>
+        <v>-4.9464</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.78</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2354</v>
+        <v>-0.2538</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.6496</v>
+        <v>-6.0912</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.58</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4248</v>
+        <v>-0.4368</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.1952</v>
+        <v>-10.4832</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.55</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4526</v>
+        <v>-0.4631</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.8624</v>
+        <v>-11.1144</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3649/event_3649_evp_summary.xlsx
+++ b/database/event/3649/event_3649_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.4079</v>
+        <v>9.0482</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3441</v>
+        <v>2.2544</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6585</v>
+        <v>3.5161</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4079</v>
+        <v>9.0482</v>
       </c>
       <c r="F2" t="n">
-        <v>3.405</v>
+        <v>3.3356</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0029</v>
+        <v>5.7125</v>
       </c>
       <c r="H2" t="n">
-        <v>6.3403</v>
+        <v>6.0808</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4237</v>
+        <v>3.4142</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0029</v>
+        <v>6.0823</v>
       </c>
       <c r="K2" t="n">
         <v>91</v>
@@ -529,7 +529,7 @@
         <v>203</v>
       </c>
       <c r="M2" t="n">
-        <v>9.426600000000001</v>
+        <v>9.496500000000001</v>
       </c>
       <c r="N2" t="n">
         <v>294</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.4359</v>
+        <v>8.3635</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1019</v>
+        <v>2.0838</v>
       </c>
       <c r="D3" t="n">
-        <v>3.216</v>
+        <v>3.2042</v>
       </c>
       <c r="E3" t="n">
-        <v>8.4359</v>
+        <v>8.3635</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4852</v>
+        <v>3.4003</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9507</v>
+        <v>4.9632</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6047</v>
+        <v>6.3236</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5665</v>
+        <v>3.5505</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9507</v>
+        <v>4.9632</v>
       </c>
       <c r="K3" t="n">
         <v>91</v>
@@ -575,7 +575,7 @@
         <v>203</v>
       </c>
       <c r="M3" t="n">
-        <v>8.517200000000001</v>
+        <v>8.5137</v>
       </c>
       <c r="N3" t="n">
         <v>294</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8183</v>
+        <v>6.4945</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6988</v>
+        <v>1.6182</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4796</v>
+        <v>2.3528</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8183</v>
+        <v>6.4945</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4585</v>
+        <v>3.3639</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3598</v>
+        <v>3.1306</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5166</v>
+        <v>6.187</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5189</v>
+        <v>3.4738</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3598</v>
+        <v>3.1306</v>
       </c>
       <c r="K4" t="n">
         <v>93</v>
@@ -621,7 +621,7 @@
         <v>182</v>
       </c>
       <c r="M4" t="n">
-        <v>6.8787</v>
+        <v>6.6044</v>
       </c>
       <c r="N4" t="n">
         <v>275</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8133</v>
+        <v>5.7447</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4484</v>
+        <v>1.4313</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0221</v>
+        <v>2.0112</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8133</v>
+        <v>5.7447</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0914</v>
+        <v>3.0544</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7219</v>
+        <v>2.6903</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3055</v>
+        <v>5.025</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8649</v>
+        <v>2.8214</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7219</v>
+        <v>2.6903</v>
       </c>
       <c r="K5" t="n">
         <v>91</v>
@@ -667,7 +667,7 @@
         <v>203</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5868</v>
+        <v>5.5117</v>
       </c>
       <c r="N5" t="n">
         <v>294</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0618</v>
+        <v>4.8705</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2612</v>
+        <v>1.2135</v>
       </c>
       <c r="D6" t="n">
-        <v>1.68</v>
+        <v>1.613</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0618</v>
+        <v>4.8705</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0362</v>
+        <v>3.8861</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0256</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>8.422700000000001</v>
+        <v>8.147600000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5482</v>
+        <v>4.5746</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0256</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>93</v>
@@ -713,7 +713,7 @@
         <v>182</v>
       </c>
       <c r="M6" t="n">
-        <v>5.573799999999999</v>
+        <v>5.559</v>
       </c>
       <c r="N6" t="n">
         <v>275</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4839</v>
+        <v>4.3284</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1172</v>
+        <v>1.0785</v>
       </c>
       <c r="D7" t="n">
-        <v>1.417</v>
+        <v>1.366</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4839</v>
+        <v>4.3284</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0187</v>
+        <v>1.8101</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4652</v>
+        <v>2.5183</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0187</v>
+        <v>1.8101</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0901</v>
+        <v>1.0163</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4652</v>
+        <v>2.5183</v>
       </c>
       <c r="K7" t="n">
         <v>91</v>
@@ -759,7 +759,7 @@
         <v>203</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5553</v>
+        <v>3.5346</v>
       </c>
       <c r="N7" t="n">
         <v>294</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2665</v>
+        <v>4.0379</v>
       </c>
       <c r="C8" t="n">
-        <v>1.063</v>
+        <v>1.0061</v>
       </c>
       <c r="D8" t="n">
-        <v>1.318</v>
+        <v>1.2337</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2665</v>
+        <v>4.0379</v>
       </c>
       <c r="F8" t="n">
-        <v>3.934</v>
+        <v>3.7992</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3325</v>
+        <v>0.2387</v>
       </c>
       <c r="H8" t="n">
-        <v>8.085699999999999</v>
+        <v>7.8211</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3662</v>
+        <v>4.3913</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3325</v>
+        <v>0.2387</v>
       </c>
       <c r="K8" t="n">
         <v>93</v>
@@ -805,7 +805,7 @@
         <v>182</v>
       </c>
       <c r="M8" t="n">
-        <v>4.698700000000001</v>
+        <v>4.63</v>
       </c>
       <c r="N8" t="n">
         <v>275</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9577</v>
+        <v>3.7591</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9861</v>
+        <v>0.9366</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1774</v>
+        <v>1.1067</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9577</v>
+        <v>3.7591</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1172</v>
+        <v>3.8954</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1595</v>
+        <v>-0.1363</v>
       </c>
       <c r="H9" t="n">
-        <v>8.6899</v>
+        <v>8.182499999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6925</v>
+        <v>4.5942</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1595</v>
+        <v>-0.1363</v>
       </c>
       <c r="K9" t="n">
         <v>150</v>
@@ -851,7 +851,7 @@
         <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>4.532999999999999</v>
+        <v>4.4579</v>
       </c>
       <c r="N9" t="n">
         <v>201</v>
@@ -860,231 +860,231 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9366</v>
+        <v>2.85</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7317</v>
+        <v>0.7101</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7126</v>
+        <v>0.6925</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9366</v>
+        <v>2.85</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3044</v>
+        <v>3.3731</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3678</v>
+        <v>-0.5231</v>
       </c>
       <c r="H10" t="n">
-        <v>6.0082</v>
+        <v>6.2214</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2444</v>
+        <v>3.4931</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3678</v>
+        <v>-0.5231</v>
       </c>
       <c r="K10" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="L10" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8766</v>
+        <v>2.97</v>
       </c>
       <c r="N10" t="n">
-        <v>229</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9041</v>
+        <v>2.7826</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7236</v>
+        <v>0.6933</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6978</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9041</v>
+        <v>2.7826</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4622</v>
+        <v>3.2207</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5581</v>
+        <v>-0.4381</v>
       </c>
       <c r="H11" t="n">
-        <v>6.5288</v>
+        <v>5.6491</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5255</v>
+        <v>3.1718</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5581</v>
+        <v>-0.4381</v>
       </c>
       <c r="K11" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9674</v>
+        <v>2.7337</v>
       </c>
       <c r="N11" t="n">
-        <v>201</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6517</v>
+        <v>2.5799</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6607</v>
+        <v>0.6428</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5829</v>
+        <v>0.5695</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6517</v>
+        <v>2.5799</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6517</v>
+        <v>2.6427</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0788</v>
+        <v>3.4791</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0788</v>
+        <v>1.9534</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0788</v>
+        <v>1.8906</v>
       </c>
       <c r="N12" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5369</v>
+        <v>2.5639</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6321</v>
+        <v>0.6388</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5306</v>
+        <v>0.5622</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5369</v>
+        <v>2.5639</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5369</v>
+        <v>2.5639</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8276</v>
+        <v>2.9256</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8276</v>
+        <v>2.9256</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8276</v>
+        <v>2.9256</v>
       </c>
       <c r="N13" t="n">
-        <v>184</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5268</v>
+        <v>2.4903</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6296</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.526</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5268</v>
+        <v>2.4903</v>
       </c>
       <c r="F14" t="n">
-        <v>2.606</v>
+        <v>2.4903</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.07920000000000001</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7039</v>
+        <v>2.757</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0001</v>
+        <v>2.757</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.07920000000000001</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="L14" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9209</v>
+        <v>2.757</v>
       </c>
       <c r="N14" t="n">
-        <v>201</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4152</v>
+        <v>2.3829</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6018</v>
+        <v>0.5937</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4752</v>
+        <v>0.4797</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4152</v>
+        <v>2.3829</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4152</v>
+        <v>2.3829</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5611</v>
+        <v>2.5107</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5611</v>
+        <v>2.5107</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5611</v>
+        <v>2.5107</v>
       </c>
       <c r="N15" t="n">
         <v>184</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3695</v>
+        <v>2.3682</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5904</v>
+        <v>0.5901</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4544</v>
+        <v>0.473</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3695</v>
+        <v>2.3682</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8081</v>
+        <v>2.8087</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4386</v>
+        <v>-0.4405</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3708</v>
+        <v>4.1023</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3602</v>
+        <v>2.3033</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4386</v>
+        <v>-0.4405</v>
       </c>
       <c r="K16" t="n">
         <v>157</v>
@@ -1173,7 +1173,7 @@
         <v>72</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9216</v>
+        <v>1.8628</v>
       </c>
       <c r="N16" t="n">
         <v>229</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3488</v>
+        <v>2.3454</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5844</v>
       </c>
       <c r="D17" t="n">
-        <v>0.445</v>
+        <v>0.4627</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3488</v>
+        <v>2.3454</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3488</v>
+        <v>2.3454</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4158</v>
+        <v>2.4248</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4158</v>
+        <v>2.4248</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4158</v>
+        <v>2.4248</v>
       </c>
       <c r="N17" t="n">
         <v>184</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1236</v>
+        <v>2.1206</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5291</v>
+        <v>0.5284</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3425</v>
+        <v>0.3602</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1236</v>
+        <v>2.1206</v>
       </c>
       <c r="F18" t="n">
         <v>2.8966</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.773</v>
+        <v>-0.776</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6628</v>
+        <v>4.4323</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5179</v>
+        <v>2.4886</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.773</v>
+        <v>-0.776</v>
       </c>
       <c r="K18" t="n">
         <v>150</v>
@@ -1265,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7449</v>
+        <v>1.7126</v>
       </c>
       <c r="N18" t="n">
         <v>201</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8716</v>
+        <v>1.5029</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4663</v>
+        <v>0.3745</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2278</v>
+        <v>0.0789</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8716</v>
+        <v>1.5029</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1832</v>
+        <v>0.9115</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6884</v>
+        <v>0.5914</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1832</v>
+        <v>0.9115</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6389</v>
+        <v>0.5118</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6884</v>
+        <v>0.5914</v>
       </c>
       <c r="K19" t="n">
         <v>157</v>
@@ -1311,7 +1311,7 @@
         <v>72</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3273</v>
+        <v>1.1032</v>
       </c>
       <c r="N19" t="n">
         <v>229</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3944</v>
+        <v>1.3562</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3474</v>
+        <v>0.3379</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0106</v>
+        <v>0.012</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3944</v>
+        <v>1.3562</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8271</v>
+        <v>1.6772</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4327</v>
+        <v>-0.321</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8271</v>
+        <v>1.6772</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9866</v>
+        <v>0.9417</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4327</v>
+        <v>-0.321</v>
       </c>
       <c r="K20" t="n">
         <v>91</v>
@@ -1357,7 +1357,7 @@
         <v>203</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5539000000000001</v>
+        <v>0.6207</v>
       </c>
       <c r="N20" t="n">
         <v>294</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0605</v>
+        <v>1.0103</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2642</v>
+        <v>0.2517</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1414</v>
+        <v>-0.1455</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0605</v>
+        <v>1.0103</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0605</v>
+        <v>1.132</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.1217</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0605</v>
+        <v>1.132</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0605</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.1217</v>
       </c>
       <c r="K21" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0605</v>
+        <v>0.5139</v>
       </c>
       <c r="N21" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.9895</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2124</v>
+        <v>0.2465</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2362</v>
+        <v>-0.155</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.9895</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9459</v>
+        <v>0.9895</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0936</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9459</v>
+        <v>0.9895</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5108</v>
+        <v>0.9895</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0936</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4172</v>
+        <v>0.9895</v>
       </c>
       <c r="N22" t="n">
-        <v>201</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6694</v>
+        <v>0.627</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1668</v>
+        <v>0.1562</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3195</v>
+        <v>-0.3202</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6694</v>
+        <v>0.627</v>
       </c>
       <c r="F23" t="n">
-        <v>0.377</v>
+        <v>0.3836</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2924</v>
+        <v>0.2434</v>
       </c>
       <c r="H23" t="n">
-        <v>0.377</v>
+        <v>0.3836</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2036</v>
+        <v>0.2154</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2924</v>
+        <v>0.2434</v>
       </c>
       <c r="K23" t="n">
         <v>93</v>
@@ -1495,7 +1495,7 @@
         <v>182</v>
       </c>
       <c r="M23" t="n">
-        <v>0.496</v>
+        <v>0.4588</v>
       </c>
       <c r="N23" t="n">
         <v>275</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6289</v>
+        <v>0.5949</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1567</v>
+        <v>0.1482</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3379</v>
+        <v>-0.3348</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6289</v>
+        <v>0.5949</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6289</v>
+        <v>0.5949</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6289</v>
+        <v>0.5949</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6289</v>
+        <v>0.5949</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6289</v>
+        <v>0.5949</v>
       </c>
       <c r="N24" t="n">
         <v>155</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4452</v>
+        <v>0.3636</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1109</v>
+        <v>0.0906</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4215</v>
+        <v>-0.4402</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4452</v>
+        <v>0.3636</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4452</v>
+        <v>0.3636</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4452</v>
+        <v>0.3636</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4452</v>
+        <v>0.3636</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4452</v>
+        <v>0.3636</v>
       </c>
       <c r="N25" t="n">
         <v>155</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4269</v>
+        <v>0.2912</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1064</v>
+        <v>0.0726</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4299</v>
+        <v>-0.4731</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4269</v>
+        <v>0.2912</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4269</v>
+        <v>0.2912</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4269</v>
+        <v>0.2912</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4269</v>
+        <v>0.2912</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4269</v>
+        <v>0.2912</v>
       </c>
       <c r="N26" t="n">
         <v>120</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3238</v>
+        <v>0.2507</v>
       </c>
       <c r="C27" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4768</v>
+        <v>-0.4916</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3238</v>
+        <v>0.2507</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3238</v>
+        <v>0.2507</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3238</v>
+        <v>0.2507</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3238</v>
+        <v>0.2507</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3238</v>
+        <v>0.2507</v>
       </c>
       <c r="N27" t="n">
         <v>120</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2675</v>
+        <v>0.2109</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0667</v>
+        <v>0.0525</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5024</v>
+        <v>-0.5097</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2675</v>
+        <v>0.2109</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2675</v>
+        <v>0.2109</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2675</v>
+        <v>0.2109</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2675</v>
+        <v>0.2109</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2675</v>
+        <v>0.2109</v>
       </c>
       <c r="N28" t="n">
         <v>86</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0206</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0166</v>
+        <v>-0.0051</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6545</v>
+        <v>-0.6152</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0206</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1745</v>
+        <v>1.2439</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.2411</v>
+        <v>-1.2645</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1745</v>
+        <v>1.2439</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6342</v>
+        <v>0.6984</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.2411</v>
+        <v>-1.2645</v>
       </c>
       <c r="K29" t="n">
         <v>93</v>
@@ -1771,7 +1771,7 @@
         <v>182</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6069000000000001</v>
+        <v>-0.5660999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>275</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2696</v>
+        <v>-0.2686</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0672</v>
+        <v>-0.0669</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7469</v>
+        <v>-0.7281</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2696</v>
+        <v>-0.2686</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2696</v>
+        <v>-0.2686</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2696</v>
+        <v>-0.2686</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2696</v>
+        <v>-0.2686</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2696</v>
+        <v>-0.2686</v>
       </c>
       <c r="N30" t="n">
         <v>184</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4296</v>
+        <v>-0.4487</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.107</v>
+        <v>-0.1118</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8198</v>
+        <v>-0.8102</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4296</v>
+        <v>-0.4487</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4296</v>
+        <v>0.0007</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.4494</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4296</v>
+        <v>0.0007</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4296</v>
+        <v>0.0004</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.4494</v>
       </c>
       <c r="K31" t="n">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4296</v>
+        <v>-0.449</v>
       </c>
       <c r="N31" t="n">
-        <v>120</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5028</v>
+        <v>-0.4654</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1253</v>
+        <v>-0.116</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8531</v>
+        <v>-0.8178</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5028</v>
+        <v>-0.4654</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.4654</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4304</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.4654</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0391</v>
+        <v>-0.4654</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4304</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="L32" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4695</v>
+        <v>-0.4654</v>
       </c>
       <c r="N32" t="n">
-        <v>229</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7113</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.178</v>
+        <v>-0.1772</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9493</v>
+        <v>-0.9298</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7113</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7113</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7113</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7113</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7113</v>
       </c>
       <c r="N33" t="n">
         <v>184</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9048</v>
+        <v>-0.9759</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2254</v>
+        <v>-0.2432</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0361</v>
+        <v>-1.0504</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9048</v>
+        <v>-0.9759</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9048</v>
+        <v>-0.9759</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9048</v>
+        <v>-0.9759</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9048</v>
+        <v>-0.9759</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9048</v>
+        <v>-0.9759</v>
       </c>
       <c r="N34" t="n">
         <v>120</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1617</v>
+        <v>-1.1062</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2894</v>
+        <v>-0.2756</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.153</v>
+        <v>-1.1097</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1617</v>
+        <v>-1.1062</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1617</v>
+        <v>-1.1062</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1617</v>
+        <v>-1.1062</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1617</v>
+        <v>-1.1062</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1617</v>
+        <v>-1.1062</v>
       </c>
       <c r="N35" t="n">
         <v>86</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3306</v>
+        <v>-1.2809</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3315</v>
+        <v>-0.3191</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2299</v>
+        <v>-1.1893</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3306</v>
+        <v>-1.2809</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3306</v>
+        <v>-1.2809</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3306</v>
+        <v>-1.2809</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3306</v>
+        <v>-1.2809</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3306</v>
+        <v>-1.2809</v>
       </c>
       <c r="N36" t="n">
         <v>86</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3412</v>
+        <v>-1.2898</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3342</v>
+        <v>-0.3214</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2347</v>
+        <v>-1.1934</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3412</v>
+        <v>-1.2898</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3412</v>
+        <v>-1.2898</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3412</v>
+        <v>-1.2898</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3412</v>
+        <v>-1.2898</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3412</v>
+        <v>-1.2898</v>
       </c>
       <c r="N37" t="n">
         <v>86</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3788</v>
+        <v>-1.3345</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3435</v>
+        <v>-0.3325</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2519</v>
+        <v>-1.2137</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3788</v>
+        <v>-1.3345</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3788</v>
+        <v>-1.3345</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3788</v>
+        <v>-1.3345</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3788</v>
+        <v>-1.3345</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3788</v>
+        <v>-1.3345</v>
       </c>
       <c r="N38" t="n">
         <v>86</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7809</v>
+        <v>-1.6221</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4437</v>
+        <v>-0.4042</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4349</v>
+        <v>-1.3447</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7809</v>
+        <v>-1.6221</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1826</v>
+        <v>-1.043</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1826</v>
+        <v>-1.043</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.5856</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="K39" t="n">
         <v>157</v>
@@ -2231,7 +2231,7 @@
         <v>72</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2369</v>
+        <v>-1.1647</v>
       </c>
       <c r="N39" t="n">
         <v>229</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.901</v>
+        <v>-1.8912</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4737</v>
+        <v>-0.4712</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4896</v>
+        <v>-1.4673</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.901</v>
+        <v>-1.8912</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.901</v>
+        <v>-1.8912</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.901</v>
+        <v>-1.8912</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.901</v>
+        <v>-1.8912</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.901</v>
+        <v>-1.8912</v>
       </c>
       <c r="N40" t="n">
         <v>120</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2075</v>
+        <v>-2.1921</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.55</v>
+        <v>-0.5462</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6291</v>
+        <v>-1.6044</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2075</v>
+        <v>-2.1921</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2075</v>
+        <v>-2.1921</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2075</v>
+        <v>-2.1921</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2075</v>
+        <v>-2.1921</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2075</v>
+        <v>-2.1921</v>
       </c>
       <c r="N41" t="n">
         <v>155</v>
@@ -2429,10 +2429,10 @@
         <v>1.55</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1904</v>
+        <v>1.2063</v>
       </c>
       <c r="J2" t="n">
-        <v>26.1888</v>
+        <v>26.5386</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.54</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1727</v>
+        <v>1.1867</v>
       </c>
       <c r="J3" t="n">
-        <v>25.7994</v>
+        <v>26.1074</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9203</v>
+        <v>0.9114</v>
       </c>
       <c r="J4" t="n">
-        <v>20.2466</v>
+        <v>20.0508</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.26</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6514</v>
+        <v>0.6274</v>
       </c>
       <c r="J5" t="n">
-        <v>14.3308</v>
+        <v>13.8028</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1731</v>
+        <v>0.1446</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8082</v>
+        <v>3.1812</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1557</v>
+        <v>0.127</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4254</v>
+        <v>2.794</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1274</v>
+        <v>0.103</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8028</v>
+        <v>2.266</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2787</v>
+        <v>-0.262</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.1314</v>
+        <v>-5.764</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.61</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.406</v>
+        <v>-0.395</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.932</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.46</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5374</v>
+        <v>-0.5413</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.8228</v>
+        <v>-11.9086</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1586</v>
+        <v>0.1412</v>
       </c>
       <c r="J12" t="n">
-        <v>4.758</v>
+        <v>4.236</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1237</v>
+        <v>0.1069</v>
       </c>
       <c r="J13" t="n">
-        <v>3.711</v>
+        <v>3.207</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1237</v>
+        <v>0.1069</v>
       </c>
       <c r="J14" t="n">
-        <v>3.711</v>
+        <v>3.207</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2169</v>
+        <v>-0.1965</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.507</v>
+        <v>-5.895</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.71</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3331</v>
+        <v>-0.3169</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.993</v>
+        <v>-9.507</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.31</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4286</v>
+        <v>0.3641</v>
       </c>
       <c r="J17" t="n">
-        <v>12.858</v>
+        <v>10.923</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4286</v>
+        <v>0.3641</v>
       </c>
       <c r="J18" t="n">
-        <v>12.858</v>
+        <v>10.923</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3371</v>
+        <v>0.2798</v>
       </c>
       <c r="J19" t="n">
-        <v>10.113</v>
+        <v>8.394</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.03</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0608</v>
+        <v>0.0434</v>
       </c>
       <c r="J20" t="n">
-        <v>1.824</v>
+        <v>1.302</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.93</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1247</v>
+        <v>-0.1062</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.741</v>
+        <v>-3.186</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.44</v>
       </c>
       <c r="I22" t="n">
-        <v>0.656</v>
+        <v>0.6977</v>
       </c>
       <c r="J22" t="n">
-        <v>18.368</v>
+        <v>19.5356</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2093</v>
+        <v>0.1928</v>
       </c>
       <c r="J23" t="n">
-        <v>5.8604</v>
+        <v>5.3984</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.174</v>
+        <v>-0.1544</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.872</v>
+        <v>-4.3232</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.68</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3595</v>
+        <v>-0.3452</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.066</v>
+        <v>-9.6656</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4661</v>
+        <v>-0.4624</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.0508</v>
+        <v>-12.9472</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5283</v>
+        <v>0.4589</v>
       </c>
       <c r="J27" t="n">
-        <v>14.7924</v>
+        <v>12.8492</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.21</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3144</v>
+        <v>0.2591</v>
       </c>
       <c r="J28" t="n">
-        <v>8.8032</v>
+        <v>7.2548</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.19</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2903</v>
+        <v>0.2375</v>
       </c>
       <c r="J29" t="n">
-        <v>8.128399999999999</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1298</v>
+        <v>0.0993</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6344</v>
+        <v>2.7804</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.171</v>
+        <v>-0.151</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.788</v>
+        <v>-4.228</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.72</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4804</v>
+        <v>1.5141</v>
       </c>
       <c r="J32" t="n">
-        <v>37.01</v>
+        <v>37.8525</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.59</v>
       </c>
       <c r="I33" t="n">
-        <v>1.261</v>
+        <v>1.2852</v>
       </c>
       <c r="J33" t="n">
-        <v>31.525</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.29</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7127</v>
+        <v>0.6915</v>
       </c>
       <c r="J34" t="n">
-        <v>17.8175</v>
+        <v>17.2875</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.631</v>
+        <v>0.606</v>
       </c>
       <c r="J35" t="n">
-        <v>15.775</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2635</v>
+        <v>-0.2304</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.5875</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.92</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1007</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.5175</v>
+        <v>-2.1625</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.87</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1594</v>
+        <v>-0.1437</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.985</v>
+        <v>-3.5925</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.87</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1594</v>
+        <v>-0.1437</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.985</v>
+        <v>-3.5925</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2602</v>
+        <v>-0.2436</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.505</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.43</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5629</v>
+        <v>-0.5707</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.0725</v>
+        <v>-14.2675</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.64</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3833</v>
+        <v>1.4187</v>
       </c>
       <c r="J42" t="n">
-        <v>35.9658</v>
+        <v>36.8862</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.51</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1489</v>
+        <v>1.1576</v>
       </c>
       <c r="J43" t="n">
-        <v>29.8714</v>
+        <v>30.0976</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.51</v>
       </c>
       <c r="I44" t="n">
-        <v>1.1489</v>
+        <v>1.1576</v>
       </c>
       <c r="J44" t="n">
-        <v>29.8714</v>
+        <v>30.0976</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.82</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5843</v>
+        <v>-0.5491</v>
       </c>
       <c r="J45" t="n">
-        <v>-15.1918</v>
+        <v>-14.2766</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8917</v>
+        <v>-0.8817</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.1842</v>
+        <v>-22.9242</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.28</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6022</v>
+        <v>0.5487</v>
       </c>
       <c r="J47" t="n">
-        <v>15.6572</v>
+        <v>14.2662</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.01</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0621</v>
+        <v>0.0434</v>
       </c>
       <c r="J48" t="n">
-        <v>1.6146</v>
+        <v>1.1284</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.76</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2806</v>
+        <v>-0.2619</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.2956</v>
+        <v>-6.8094</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.337</v>
+        <v>-0.3209</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.762</v>
+        <v>-8.343400000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3462</v>
+        <v>-0.3307</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.001200000000001</v>
+        <v>-8.5982</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.53</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9949</v>
+        <v>0.9821</v>
       </c>
       <c r="J52" t="n">
-        <v>22.8827</v>
+        <v>22.5883</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.43</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8569</v>
+        <v>0.8415</v>
       </c>
       <c r="J53" t="n">
-        <v>19.7087</v>
+        <v>19.3545</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6089</v>
+        <v>0.5991</v>
       </c>
       <c r="J54" t="n">
-        <v>14.0047</v>
+        <v>13.7793</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.036</v>
+        <v>-0.0305</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.828</v>
+        <v>-0.7015</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.85</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.4708</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.7208</v>
+        <v>-10.8284</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.08</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2574</v>
+        <v>0.2141</v>
       </c>
       <c r="J57" t="n">
-        <v>5.9202</v>
+        <v>4.9243</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.99</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0062</v>
+        <v>-0.0018</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.1426</v>
+        <v>-0.0414</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0245</v>
+        <v>-0.0172</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.5635</v>
+        <v>-0.3956</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.7</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.33</v>
+        <v>-0.3138</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.59</v>
+        <v>-7.2174</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.36</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6267</v>
+        <v>-0.6461</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.4141</v>
+        <v>-14.8603</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.39</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8095</v>
+        <v>0.7935</v>
       </c>
       <c r="J62" t="n">
-        <v>22.666</v>
+        <v>22.218</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.23</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5684</v>
+        <v>0.5591</v>
       </c>
       <c r="J63" t="n">
-        <v>15.9152</v>
+        <v>15.6548</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4715</v>
+        <v>0.4466</v>
       </c>
       <c r="J64" t="n">
-        <v>13.202</v>
+        <v>12.5048</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.15</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4355</v>
+        <v>0.4019</v>
       </c>
       <c r="J65" t="n">
-        <v>12.194</v>
+        <v>11.2532</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4259</v>
+        <v>-0.3842</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.9252</v>
+        <v>-10.7576</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.073</v>
+        <v>-0.061</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.044</v>
+        <v>-1.708</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.135</v>
+        <v>-0.1191</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.78</v>
+        <v>-3.3348</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.89</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1463</v>
+        <v>-0.1299</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.0964</v>
+        <v>-3.6372</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2281</v>
+        <v>-0.2093</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.3868</v>
+        <v>-5.8604</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.68</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.351</v>
+        <v>-0.3358</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.827999999999999</v>
+        <v>-9.4024</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>1.5363</v>
+        <v>1.5578</v>
       </c>
       <c r="J72" t="n">
-        <v>29.1897</v>
+        <v>29.5982</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.5</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9212</v>
+        <v>0.911</v>
       </c>
       <c r="J73" t="n">
-        <v>17.5028</v>
+        <v>17.309</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.42</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8171</v>
+        <v>0.8078</v>
       </c>
       <c r="J74" t="n">
-        <v>15.5249</v>
+        <v>15.3482</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.26</v>
       </c>
       <c r="I75" t="n">
-        <v>0.589</v>
+        <v>0.586</v>
       </c>
       <c r="J75" t="n">
-        <v>11.191</v>
+        <v>11.134</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.96</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2416</v>
+        <v>-0.2124</v>
       </c>
       <c r="J76" t="n">
-        <v>-4.5904</v>
+        <v>-4.0356</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.05</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2306</v>
+        <v>0.2004</v>
       </c>
       <c r="J77" t="n">
-        <v>4.3814</v>
+        <v>3.8076</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.04</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2054</v>
+        <v>0.1775</v>
       </c>
       <c r="J78" t="n">
-        <v>3.9026</v>
+        <v>3.3725</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.6</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4083</v>
+        <v>-0.3978</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.7577</v>
+        <v>-7.5582</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.59</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4172</v>
+        <v>-0.4073</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.9268</v>
+        <v>-7.7387</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.32</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6742</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.3823</v>
+        <v>-12.8098</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6034</v>
+        <v>0.6409</v>
       </c>
       <c r="J82" t="n">
-        <v>18.102</v>
+        <v>19.227</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.21</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3553</v>
+        <v>0.3478</v>
       </c>
       <c r="J83" t="n">
-        <v>10.659</v>
+        <v>10.434</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1459</v>
+        <v>-0.1264</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.377</v>
+        <v>-3.792</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2612</v>
+        <v>-0.2416</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.836</v>
+        <v>-7.248</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.58</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4537</v>
+        <v>-0.4492</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.611</v>
+        <v>-13.476</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4189</v>
+        <v>0.3552</v>
       </c>
       <c r="J87" t="n">
-        <v>12.567</v>
+        <v>10.656</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2351</v>
+        <v>0.1869</v>
       </c>
       <c r="J88" t="n">
-        <v>7.053</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.02</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0499</v>
+        <v>0.0346</v>
       </c>
       <c r="J89" t="n">
-        <v>1.497</v>
+        <v>1.038</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.01</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0273</v>
+        <v>0.0181</v>
       </c>
       <c r="J90" t="n">
-        <v>0.819</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.87</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1859</v>
+        <v>-0.1654</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.577</v>
+        <v>-4.962</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.66</v>
       </c>
       <c r="I92" t="n">
-        <v>1.166</v>
+        <v>1.1612</v>
       </c>
       <c r="J92" t="n">
-        <v>26.818</v>
+        <v>26.7076</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.29</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6532</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="J93" t="n">
-        <v>15.0236</v>
+        <v>14.7568</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.14</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4063</v>
+        <v>0.3729</v>
       </c>
       <c r="J94" t="n">
-        <v>9.344900000000001</v>
+        <v>8.576700000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.134</v>
+        <v>0.1105</v>
       </c>
       <c r="J95" t="n">
-        <v>3.082</v>
+        <v>2.5415</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.98</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1387</v>
+        <v>-0.1117</v>
       </c>
       <c r="J96" t="n">
-        <v>-3.1901</v>
+        <v>-2.5691</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4079</v>
+        <v>0.3564</v>
       </c>
       <c r="J97" t="n">
-        <v>9.3817</v>
+        <v>8.1972</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.9</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.135</v>
+        <v>-0.1191</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.105</v>
+        <v>-2.7393</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.83</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2084</v>
+        <v>-0.1899</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.7932</v>
+        <v>-4.3677</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2572</v>
+        <v>-0.2385</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.9156</v>
+        <v>-5.4855</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4581</v>
+        <v>-0.4526</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.5363</v>
+        <v>-10.4098</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4494</v>
+        <v>0.3924</v>
       </c>
       <c r="J102" t="n">
-        <v>12.5832</v>
+        <v>10.9872</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0074</v>
+        <v>0.0045</v>
       </c>
       <c r="J103" t="n">
-        <v>0.2072</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.95</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0824</v>
+        <v>-0.0683</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.3072</v>
+        <v>-1.9124</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.79</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2567</v>
+        <v>-0.237</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.1876</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.76</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2858</v>
+        <v>-0.267</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.0024</v>
+        <v>-7.476</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7574</v>
+        <v>0.7296</v>
       </c>
       <c r="J107" t="n">
-        <v>21.2072</v>
+        <v>20.4288</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.23</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6118</v>
+        <v>0.5778</v>
       </c>
       <c r="J108" t="n">
-        <v>17.1304</v>
+        <v>16.1784</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5474</v>
+        <v>0.5121</v>
       </c>
       <c r="J109" t="n">
-        <v>15.3272</v>
+        <v>14.3388</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.11</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3394</v>
+        <v>0.3053</v>
       </c>
       <c r="J110" t="n">
-        <v>9.5032</v>
+        <v>8.548400000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1733</v>
+        <v>0.1468</v>
       </c>
       <c r="J111" t="n">
-        <v>4.8524</v>
+        <v>4.1104</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.43</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8468</v>
+        <v>0.8094</v>
       </c>
       <c r="J112" t="n">
-        <v>22.0168</v>
+        <v>21.0444</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.98</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0323</v>
+        <v>-0.0249</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.8398</v>
+        <v>-0.6474</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.82</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2208</v>
+        <v>-0.2014</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.7408</v>
+        <v>-5.2364</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.345</v>
+        <v>-0.3294</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.970000000000001</v>
+        <v>-8.564399999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.46</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.547</v>
+        <v>-0.5538</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.222</v>
+        <v>-14.3988</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.46</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0469</v>
+        <v>1.0519</v>
       </c>
       <c r="J117" t="n">
-        <v>27.2194</v>
+        <v>27.3494</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7116</v>
+        <v>0.6825</v>
       </c>
       <c r="J118" t="n">
-        <v>18.5016</v>
+        <v>17.745</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.629</v>
+        <v>0.5968</v>
       </c>
       <c r="J119" t="n">
-        <v>16.354</v>
+        <v>15.5168</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.16</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4563</v>
+        <v>0.4218</v>
       </c>
       <c r="J120" t="n">
-        <v>11.8638</v>
+        <v>10.9668</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.433</v>
+        <v>-0.3923</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.258</v>
+        <v>-10.1998</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8069</v>
+        <v>0.7813</v>
       </c>
       <c r="J122" t="n">
-        <v>24.207</v>
+        <v>23.439</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.27</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7036</v>
+        <v>0.6717</v>
       </c>
       <c r="J123" t="n">
-        <v>21.108</v>
+        <v>20.151</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.23</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6186</v>
+        <v>0.5831</v>
       </c>
       <c r="J124" t="n">
-        <v>18.558</v>
+        <v>17.493</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.12</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3698</v>
+        <v>0.3333</v>
       </c>
       <c r="J125" t="n">
-        <v>11.094</v>
+        <v>9.999000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.76</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7052</v>
+        <v>-0.6752</v>
       </c>
       <c r="J126" t="n">
-        <v>-21.156</v>
+        <v>-20.256</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.17</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3814</v>
+        <v>0.3259</v>
       </c>
       <c r="J127" t="n">
-        <v>11.442</v>
+        <v>9.776999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.08</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2121</v>
+        <v>0.1698</v>
       </c>
       <c r="J128" t="n">
-        <v>6.363</v>
+        <v>5.094</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1913</v>
+        <v>0.1514</v>
       </c>
       <c r="J129" t="n">
-        <v>5.739</v>
+        <v>4.542</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.99</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0253</v>
+        <v>-0.0182</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.759</v>
+        <v>-0.546</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.7</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3479</v>
+        <v>-0.3331</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.437</v>
+        <v>-9.993</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.77</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4433</v>
+        <v>1.4723</v>
       </c>
       <c r="J132" t="n">
-        <v>31.7526</v>
+        <v>32.3906</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.69</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3414</v>
+        <v>1.3633</v>
       </c>
       <c r="J133" t="n">
-        <v>29.5108</v>
+        <v>29.9926</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2729</v>
+        <v>0.2419</v>
       </c>
       <c r="J134" t="n">
-        <v>6.0038</v>
+        <v>5.3218</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3913</v>
+        <v>-0.352</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.608599999999999</v>
+        <v>-7.744</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.88</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4434</v>
+        <v>-0.4044</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.754799999999999</v>
+        <v>-8.896800000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.28</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6525</v>
+        <v>0.6135</v>
       </c>
       <c r="J137" t="n">
-        <v>14.355</v>
+        <v>13.497</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.96</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0484</v>
+        <v>-0.0374</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.0648</v>
+        <v>-0.8228</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.61</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4067</v>
+        <v>-0.3957</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.9474</v>
+        <v>-8.705399999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.55</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4598</v>
+        <v>-0.4539</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.1156</v>
+        <v>-9.985799999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5034</v>
+        <v>-0.5028</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.0748</v>
+        <v>-11.0616</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.03</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1383</v>
+        <v>0.1081</v>
       </c>
       <c r="J142" t="n">
-        <v>3.4575</v>
+        <v>2.7025</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0699</v>
+        <v>-0.0581</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.7475</v>
+        <v>-1.4525</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1087</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.7175</v>
+        <v>-2.3575</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.67</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3577</v>
+        <v>-0.343</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.942500000000001</v>
+        <v>-8.574999999999999</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.55</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4646</v>
+        <v>-0.4596</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.615</v>
+        <v>-11.49</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.74</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3953</v>
+        <v>1.4202</v>
       </c>
       <c r="J147" t="n">
-        <v>34.8825</v>
+        <v>35.505</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8337</v>
+        <v>0.8163</v>
       </c>
       <c r="J148" t="n">
-        <v>20.8425</v>
+        <v>20.4075</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.33</v>
       </c>
       <c r="I149" t="n">
-        <v>0.7955</v>
+        <v>0.776</v>
       </c>
       <c r="J149" t="n">
-        <v>19.8875</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.21</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5532</v>
+        <v>0.524</v>
       </c>
       <c r="J150" t="n">
-        <v>13.83</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.91</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3711</v>
+        <v>-0.3331</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.2775</v>
+        <v>-8.327500000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.98</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.1764</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0403</v>
+        <v>-0.0282</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.5921999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3481</v>
+        <v>-0.3339</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.3101</v>
+        <v>-7.0119</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.55</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4551</v>
+        <v>-0.4486</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.5571</v>
+        <v>-9.4206</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4639</v>
+        <v>-0.4583</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.741899999999999</v>
+        <v>-9.6243</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.75</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3832</v>
+        <v>1.4073</v>
       </c>
       <c r="J157" t="n">
-        <v>29.0472</v>
+        <v>29.5533</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.71</v>
       </c>
       <c r="I158" t="n">
-        <v>1.334</v>
+        <v>1.3556</v>
       </c>
       <c r="J158" t="n">
-        <v>28.014</v>
+        <v>28.4676</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.41</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9315</v>
+        <v>0.9277</v>
       </c>
       <c r="J159" t="n">
-        <v>19.5615</v>
+        <v>19.4817</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.19</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4905</v>
+        <v>0.4612</v>
       </c>
       <c r="J160" t="n">
-        <v>10.3005</v>
+        <v>9.6852</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.1</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2735</v>
+        <v>0.2409</v>
       </c>
       <c r="J161" t="n">
-        <v>5.7435</v>
+        <v>5.0589</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1589</v>
+        <v>1.1723</v>
       </c>
       <c r="J162" t="n">
-        <v>28.9725</v>
+        <v>29.3075</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.19</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5239</v>
+        <v>0.4895</v>
       </c>
       <c r="J163" t="n">
-        <v>13.0975</v>
+        <v>12.2375</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.13</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3858</v>
+        <v>0.3516</v>
       </c>
       <c r="J164" t="n">
-        <v>9.645</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2567</v>
+        <v>0.2257</v>
       </c>
       <c r="J165" t="n">
-        <v>6.4175</v>
+        <v>5.6425</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1997</v>
+        <v>0.1715</v>
       </c>
       <c r="J166" t="n">
-        <v>4.9925</v>
+        <v>4.2875</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.26</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5616</v>
+        <v>0.5058</v>
       </c>
       <c r="J167" t="n">
-        <v>14.04</v>
+        <v>12.645</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.15</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3692</v>
+        <v>0.3154</v>
       </c>
       <c r="J168" t="n">
-        <v>9.23</v>
+        <v>7.885</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2338</v>
+        <v>-0.2139</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.845</v>
+        <v>-5.3475</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3204</v>
+        <v>-0.3034</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.01</v>
+        <v>-7.585</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.6</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4291</v>
+        <v>-0.421</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.7275</v>
+        <v>-10.525</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.82</v>
       </c>
       <c r="I172" t="n">
-        <v>1.5035</v>
+        <v>1.5371</v>
       </c>
       <c r="J172" t="n">
-        <v>33.077</v>
+        <v>33.8162</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.66</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3005</v>
+        <v>1.3199</v>
       </c>
       <c r="J173" t="n">
-        <v>28.611</v>
+        <v>29.0378</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>0.216</v>
+        <v>0.1868</v>
       </c>
       <c r="J174" t="n">
-        <v>4.752</v>
+        <v>4.1096</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1869</v>
+        <v>0.1591</v>
       </c>
       <c r="J175" t="n">
-        <v>4.1118</v>
+        <v>3.5002</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.5122</v>
+        <v>-14.9358</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1934</v>
+        <v>0.1569</v>
       </c>
       <c r="J177" t="n">
-        <v>4.2548</v>
+        <v>3.4518</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0537</v>
+        <v>-0.0429</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.1814</v>
+        <v>-0.9438</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2633</v>
+        <v>-0.2454</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.7926</v>
+        <v>-5.3988</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3009</v>
+        <v>-0.2837</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.6198</v>
+        <v>-6.2414</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.54</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4719</v>
+        <v>-0.4676</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.3818</v>
+        <v>-10.2872</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.13</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2667</v>
+        <v>0.2542</v>
       </c>
       <c r="J182" t="n">
-        <v>6.6675</v>
+        <v>6.355</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.86</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1804</v>
+        <v>-0.1617</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.51</v>
+        <v>-4.0425</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.83</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.211</v>
+        <v>-0.1916</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.275</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2408</v>
+        <v>-0.2214</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.02</v>
+        <v>-5.535</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.77</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.27</v>
+        <v>-0.2511</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.75</v>
+        <v>-6.2775</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.53</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6542</v>
+        <v>0.5823</v>
       </c>
       <c r="J187" t="n">
-        <v>16.355</v>
+        <v>14.5575</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.3</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4123</v>
+        <v>0.3497</v>
       </c>
       <c r="J188" t="n">
-        <v>10.3075</v>
+        <v>8.7425</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.29</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4012</v>
+        <v>0.3394</v>
       </c>
       <c r="J189" t="n">
-        <v>10.03</v>
+        <v>8.484999999999999</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.155</v>
+        <v>0.121</v>
       </c>
       <c r="J190" t="n">
-        <v>3.875</v>
+        <v>3.025</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2392</v>
+        <v>-0.2204</v>
       </c>
       <c r="J191" t="n">
-        <v>-5.98</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.47</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0578</v>
+        <v>1.0645</v>
       </c>
       <c r="J192" t="n">
-        <v>29.6184</v>
+        <v>29.806</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.32</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7889</v>
+        <v>0.7647</v>
       </c>
       <c r="J193" t="n">
-        <v>22.0892</v>
+        <v>21.4116</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.19</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5214</v>
+        <v>0.4881</v>
       </c>
       <c r="J194" t="n">
-        <v>14.5992</v>
+        <v>13.6668</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.18</v>
       </c>
       <c r="I195" t="n">
-        <v>0.4992</v>
+        <v>0.4657</v>
       </c>
       <c r="J195" t="n">
-        <v>13.9776</v>
+        <v>13.0396</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.95</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2411</v>
+        <v>-0.2049</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.7508</v>
+        <v>-5.7372</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.34</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6957</v>
+        <v>0.6453</v>
       </c>
       <c r="J197" t="n">
-        <v>19.4796</v>
+        <v>18.0684</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0508</v>
+        <v>-0.0409</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.4224</v>
+        <v>-1.1452</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0791</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.2148</v>
+        <v>-1.8508</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2816</v>
+        <v>-0.2629</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.8848</v>
+        <v>-7.3612</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.47</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5404</v>
+        <v>-0.5465</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.1312</v>
+        <v>-15.302</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.21</v>
       </c>
       <c r="I202" t="n">
-        <v>1.8919</v>
+        <v>1.9586</v>
       </c>
       <c r="J202" t="n">
-        <v>37.838</v>
+        <v>39.172</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.94</v>
       </c>
       <c r="I203" t="n">
-        <v>1.586</v>
+        <v>1.6243</v>
       </c>
       <c r="J203" t="n">
-        <v>31.72</v>
+        <v>32.486</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.66</v>
       </c>
       <c r="I204" t="n">
-        <v>1.2547</v>
+        <v>1.2769</v>
       </c>
       <c r="J204" t="n">
-        <v>25.094</v>
+        <v>25.538</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.05</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1131</v>
+        <v>0.0814</v>
       </c>
       <c r="J205" t="n">
-        <v>2.262</v>
+        <v>1.628</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.0919</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.788</v>
+        <v>-1.838</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.85</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.1266</v>
+        <v>-0.1007</v>
       </c>
       <c r="J207" t="n">
-        <v>-2.532</v>
+        <v>-2.014</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.79</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1962</v>
+        <v>-0.1763</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.924</v>
+        <v>-3.526</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.53</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.4472</v>
+        <v>-0.4428</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.944000000000001</v>
+        <v>-8.856</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.36</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5969</v>
+        <v>-0.6073</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.938</v>
+        <v>-12.146</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.24</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7044</v>
+        <v>-0.7347</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.088</v>
+        <v>-14.694</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.05</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1999</v>
+        <v>0.1641</v>
       </c>
       <c r="J212" t="n">
-        <v>4.3978</v>
+        <v>3.6102</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.8</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2339</v>
+        <v>-0.2167</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.1458</v>
+        <v>-4.7674</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2524</v>
+        <v>-0.2351</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.5528</v>
+        <v>-5.1722</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.73</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.299</v>
+        <v>-0.2821</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.578</v>
+        <v>-6.2062</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.417</v>
+        <v>-0.4069</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.173999999999999</v>
+        <v>-8.9518</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.49</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0705</v>
+        <v>1.0801</v>
       </c>
       <c r="J217" t="n">
-        <v>23.551</v>
+        <v>23.7622</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.41</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9455</v>
+        <v>0.9372</v>
       </c>
       <c r="J218" t="n">
-        <v>20.801</v>
+        <v>20.6184</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.34</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8146</v>
+        <v>0.7961</v>
       </c>
       <c r="J219" t="n">
-        <v>17.9212</v>
+        <v>17.5142</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.19</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5091</v>
+        <v>0.4788</v>
       </c>
       <c r="J220" t="n">
-        <v>11.2002</v>
+        <v>10.5336</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.11</v>
       </c>
       <c r="I221" t="n">
-        <v>0.3186</v>
+        <v>0.2867</v>
       </c>
       <c r="J221" t="n">
-        <v>7.0092</v>
+        <v>6.3074</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.78</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.2291</v>
+        <v>-0.2143</v>
       </c>
       <c r="J222" t="n">
-        <v>-4.582</v>
+        <v>-4.286</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.76</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2497</v>
+        <v>-0.2359</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.994</v>
+        <v>-4.718</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.57</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.423</v>
+        <v>-0.4149</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.298</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.423</v>
+        <v>-0.4149</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.298</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.47</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5109</v>
+        <v>-0.5102</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.218</v>
+        <v>-10.204</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.85</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4862</v>
+        <v>1.5174</v>
       </c>
       <c r="J227" t="n">
-        <v>29.724</v>
+        <v>30.348</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.58</v>
       </c>
       <c r="I228" t="n">
-        <v>1.1598</v>
+        <v>1.1794</v>
       </c>
       <c r="J228" t="n">
-        <v>23.196</v>
+        <v>23.588</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.49</v>
       </c>
       <c r="I229" t="n">
-        <v>1.0467</v>
+        <v>1.0619</v>
       </c>
       <c r="J229" t="n">
-        <v>20.934</v>
+        <v>21.238</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.44</v>
       </c>
       <c r="I230" t="n">
-        <v>0.9714</v>
+        <v>0.9771</v>
       </c>
       <c r="J230" t="n">
-        <v>19.428</v>
+        <v>19.542</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.33</v>
       </c>
       <c r="I231" t="n">
-        <v>0.7678</v>
+        <v>0.7547</v>
       </c>
       <c r="J231" t="n">
-        <v>15.356</v>
+        <v>15.094</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>2.09</v>
       </c>
       <c r="I232" t="n">
-        <v>1.7736</v>
+        <v>1.8287</v>
       </c>
       <c r="J232" t="n">
-        <v>33.6984</v>
+        <v>34.7453</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.53</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1011</v>
+        <v>1.1185</v>
       </c>
       <c r="J233" t="n">
-        <v>20.9209</v>
+        <v>21.2515</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.51</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0757</v>
+        <v>1.0919</v>
       </c>
       <c r="J234" t="n">
-        <v>20.4383</v>
+        <v>20.7461</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.37</v>
       </c>
       <c r="I235" t="n">
-        <v>0.851</v>
+        <v>0.843</v>
       </c>
       <c r="J235" t="n">
-        <v>16.169</v>
+        <v>16.017</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.96</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2504</v>
+        <v>-0.2232</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.7576</v>
+        <v>-4.2408</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.78</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.2157</v>
+        <v>-0.1988</v>
       </c>
       <c r="J237" t="n">
-        <v>-4.0983</v>
+        <v>-3.7772</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.76</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2371</v>
+        <v>-0.2218</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.5049</v>
+        <v>-4.2142</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.63</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3653</v>
+        <v>-0.3573</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.9407</v>
+        <v>-6.7887</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.4</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5653</v>
+        <v>-0.5713</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.7407</v>
+        <v>-10.8547</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.33</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6274</v>
+        <v>-0.6431</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.9206</v>
+        <v>-12.2189</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.38</v>
       </c>
       <c r="I242" t="n">
-        <v>0.9383</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="J242" t="n">
-        <v>26.2724</v>
+        <v>25.8972</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.33</v>
       </c>
       <c r="I243" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8146</v>
       </c>
       <c r="J243" t="n">
-        <v>23.4696</v>
+        <v>22.8088</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.19</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5384</v>
+        <v>0.4992</v>
       </c>
       <c r="J244" t="n">
-        <v>15.0752</v>
+        <v>13.9776</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.82</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5609</v>
+        <v>-0.5216</v>
       </c>
       <c r="J245" t="n">
-        <v>-15.7052</v>
+        <v>-14.6048</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.78</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6532</v>
+        <v>-0.6186</v>
       </c>
       <c r="J246" t="n">
-        <v>-18.2896</v>
+        <v>-17.3208</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.19</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4239</v>
+        <v>0.3669</v>
       </c>
       <c r="J247" t="n">
-        <v>11.8692</v>
+        <v>10.2732</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.17</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3888</v>
+        <v>0.333</v>
       </c>
       <c r="J248" t="n">
-        <v>10.8864</v>
+        <v>9.324</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0469</v>
+        <v>0.0313</v>
       </c>
       <c r="J249" t="n">
-        <v>1.3132</v>
+        <v>0.8764</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.279</v>
+        <v>-0.26</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.812</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.71</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3357</v>
+        <v>-0.3199</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.3996</v>
+        <v>-8.9572</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.47</v>
       </c>
       <c r="I252" t="n">
-        <v>0.86</v>
+        <v>0.8134</v>
       </c>
       <c r="J252" t="n">
-        <v>25.8</v>
+        <v>24.402</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.23</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4877</v>
+        <v>0.4291</v>
       </c>
       <c r="J253" t="n">
-        <v>14.631</v>
+        <v>12.873</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.05</v>
       </c>
       <c r="I254" t="n">
-        <v>0.15</v>
+        <v>0.1153</v>
       </c>
       <c r="J254" t="n">
-        <v>4.5</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3556</v>
+        <v>-0.3413</v>
       </c>
       <c r="J255" t="n">
-        <v>-10.668</v>
+        <v>-10.239</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.49</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5303</v>
+        <v>-0.5362</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.909</v>
+        <v>-16.086</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.49</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1064</v>
+        <v>1.1185</v>
       </c>
       <c r="J257" t="n">
-        <v>33.192</v>
+        <v>33.555</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.27</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7055</v>
+        <v>0.6734</v>
       </c>
       <c r="J258" t="n">
-        <v>21.165</v>
+        <v>20.202</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.08</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2677</v>
+        <v>0.2346</v>
       </c>
       <c r="J259" t="n">
-        <v>8.031000000000001</v>
+        <v>7.038</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.96</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.193</v>
+        <v>-0.1584</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.79</v>
+        <v>-4.752</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.86</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4704</v>
+        <v>-0.4288</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.112</v>
+        <v>-12.864</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.19</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4331</v>
+        <v>0.3765</v>
       </c>
       <c r="J262" t="n">
-        <v>11.6937</v>
+        <v>10.1655</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.03</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1102</v>
+        <v>0.0813</v>
       </c>
       <c r="J263" t="n">
-        <v>2.9754</v>
+        <v>2.1951</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.021</v>
+        <v>-0.0156</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.4212</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.92</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1187</v>
+        <v>-0.1016</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.2049</v>
+        <v>-2.7432</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.55</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4753</v>
+        <v>-0.4728</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.8331</v>
+        <v>-12.7656</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.45</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0514</v>
+        <v>1.0574</v>
       </c>
       <c r="J267" t="n">
-        <v>28.3878</v>
+        <v>28.5498</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.22</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6005</v>
+        <v>0.5637</v>
       </c>
       <c r="J268" t="n">
-        <v>16.2135</v>
+        <v>15.2199</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.09</v>
       </c>
       <c r="I269" t="n">
-        <v>0.296</v>
+        <v>0.2612</v>
       </c>
       <c r="J269" t="n">
-        <v>7.992</v>
+        <v>7.0524</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0814</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J270" t="n">
-        <v>2.1978</v>
+        <v>1.7334</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.83</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5414</v>
+        <v>-0.5017</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.6178</v>
+        <v>-13.5459</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9507</v>
+        <v>0.9395</v>
       </c>
       <c r="J272" t="n">
-        <v>27.5703</v>
+        <v>27.2455</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.37</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8939</v>
+        <v>0.8762</v>
       </c>
       <c r="J273" t="n">
-        <v>25.9231</v>
+        <v>25.4098</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>0.8546</v>
+        <v>0.8337</v>
       </c>
       <c r="J274" t="n">
-        <v>24.7834</v>
+        <v>24.1773</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.22</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5885</v>
+        <v>0.5547</v>
       </c>
       <c r="J275" t="n">
-        <v>17.0665</v>
+        <v>16.0863</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.62</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.0088</v>
+        <v>-1.0117</v>
       </c>
       <c r="J276" t="n">
-        <v>-29.2552</v>
+        <v>-29.3393</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.21</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4583</v>
+        <v>0.4004</v>
       </c>
       <c r="J277" t="n">
-        <v>13.2907</v>
+        <v>11.6116</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.07</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1968</v>
+        <v>0.1558</v>
       </c>
       <c r="J278" t="n">
-        <v>5.7072</v>
+        <v>4.5182</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.04</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1291</v>
+        <v>0.0974</v>
       </c>
       <c r="J279" t="n">
-        <v>3.7439</v>
+        <v>2.8246</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2397</v>
+        <v>-0.2195</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.9513</v>
+        <v>-6.3655</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.72</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3264</v>
+        <v>-0.3099</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.4656</v>
+        <v>-8.9871</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.52</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1386</v>
+        <v>1.1516</v>
       </c>
       <c r="J282" t="n">
-        <v>30.7422</v>
+        <v>31.0932</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.19</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5266</v>
+        <v>0.4906</v>
       </c>
       <c r="J283" t="n">
-        <v>14.2182</v>
+        <v>13.2462</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.12</v>
       </c>
       <c r="I284" t="n">
-        <v>0.3657</v>
+        <v>0.3307</v>
       </c>
       <c r="J284" t="n">
-        <v>9.873900000000001</v>
+        <v>8.928900000000001</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.08</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2616</v>
+        <v>0.2299</v>
       </c>
       <c r="J285" t="n">
-        <v>7.0632</v>
+        <v>6.2073</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2624</v>
+        <v>-0.2238</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.0848</v>
+        <v>-6.0426</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9409</v>
       </c>
       <c r="J287" t="n">
-        <v>26.1711</v>
+        <v>25.4043</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.93</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1066</v>
+        <v>-0.0906</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.8782</v>
+        <v>-2.4462</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1949</v>
+        <v>-0.1749</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.2623</v>
+        <v>-4.7223</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.67</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3684</v>
+        <v>-0.3548</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.9468</v>
+        <v>-9.579599999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.66</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3775</v>
+        <v>-0.3646</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.1925</v>
+        <v>-9.844200000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.84</v>
       </c>
       <c r="I292" t="n">
-        <v>1.5019</v>
+        <v>1.5336</v>
       </c>
       <c r="J292" t="n">
-        <v>30.038</v>
+        <v>30.672</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.45</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0012</v>
+        <v>1.0042</v>
       </c>
       <c r="J293" t="n">
-        <v>20.024</v>
+        <v>20.084</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.34</v>
       </c>
       <c r="I294" t="n">
-        <v>0.8072</v>
+        <v>0.7922</v>
       </c>
       <c r="J294" t="n">
-        <v>16.144</v>
+        <v>15.844</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.4519</v>
+        <v>0.4212</v>
       </c>
       <c r="J295" t="n">
-        <v>9.038</v>
+        <v>8.423999999999999</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.13</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3566</v>
+        <v>0.3245</v>
       </c>
       <c r="J296" t="n">
-        <v>7.132</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.83</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1968</v>
+        <v>-0.1812</v>
       </c>
       <c r="J297" t="n">
-        <v>-3.936</v>
+        <v>-3.624</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.83</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1968</v>
+        <v>-0.1812</v>
       </c>
       <c r="J298" t="n">
-        <v>-3.936</v>
+        <v>-3.624</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.78</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2474</v>
+        <v>-0.2321</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.948</v>
+        <v>-4.642</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.65</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3654</v>
+        <v>-0.3521</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.308</v>
+        <v>-7.042</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.58</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4279</v>
+        <v>-0.4188</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.558</v>
+        <v>-8.375999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.66</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3069</v>
+        <v>1.3269</v>
       </c>
       <c r="J302" t="n">
-        <v>31.3656</v>
+        <v>31.8456</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.27</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6848</v>
+        <v>0.6569</v>
       </c>
       <c r="J303" t="n">
-        <v>16.4352</v>
+        <v>15.7656</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.19</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5179</v>
+        <v>0.4858</v>
       </c>
       <c r="J304" t="n">
-        <v>12.4296</v>
+        <v>11.6592</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.13</v>
       </c>
       <c r="I305" t="n">
-        <v>0.3783</v>
+        <v>0.3454</v>
       </c>
       <c r="J305" t="n">
-        <v>9.0792</v>
+        <v>8.2896</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.99</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1017</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J306" t="n">
-        <v>-2.4408</v>
+        <v>-1.9488</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.31</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6874</v>
+        <v>0.6461</v>
       </c>
       <c r="J307" t="n">
-        <v>16.4976</v>
+        <v>15.5064</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.83</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2061</v>
+        <v>-0.1888</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.9464</v>
+        <v>-4.5312</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.78</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2538</v>
+        <v>-0.2359</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.0912</v>
+        <v>-5.6616</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.58</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4368</v>
+        <v>-0.4286</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.4832</v>
+        <v>-10.2864</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.55</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4631</v>
+        <v>-0.4578</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.1144</v>
+        <v>-10.9872</v>
       </c>
     </row>
   </sheetData>
